--- a/data/raw/gpt_labeled_sample.xlsx
+++ b/data/raw/gpt_labeled_sample.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N101"/>
+  <dimension ref="A1:N100"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -712,57 +712,101 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>12861</v>
+        <v>2023</v>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Галерея Плюс</t>
+          <t xml:space="preserve">Сарма </t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>3 звезды</t>
-        </is>
-      </c>
-      <c r="D5" t="inlineStr"/>
-      <c r="E5" t="inlineStr"/>
-      <c r="F5" t="inlineStr"/>
-      <c r="G5" t="inlineStr"/>
-      <c r="H5" t="inlineStr"/>
-      <c r="I5" t="inlineStr"/>
-      <c r="J5" t="inlineStr"/>
-      <c r="K5" t="inlineStr"/>
-      <c r="L5" t="inlineStr"/>
-      <c r="M5" t="inlineStr"/>
-      <c r="N5" t="inlineStr"/>
+          <t>1.0</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>К качеству товара претензий нет, но крайне возмутила работа салона! Во-первых, сначала обманули при оформлении заказа - случайно посчитали не тот матрас, естественно дороже 🤷🏻‍♀️ будьте внимательнее при оплате. Во-вторых, не предупредив меня самостоятельно перенесли доставку на другой день. В-третьих, сотрудник Наталья выдумывает разговоры и принимает решения за клиента. Обещали привезти кровать и матрас в один день, в итоге привезли одну кровать, а матрас, как утверждают сотрудники, я сказала заказать на производство 🙄 В-четвёртых, не предупреждают о том, что подъем платный, стоимость подъема из уст сотрудников разнится. Офис говорит 300р, одни грузчики 400, а вторые- 240 🤷🏻‍♀️ Надежда пыталась урегулировать ситуацию и компенсировала расходы на повторную доставку. В общем, я очень расстроена и даже зла на этот офис. Не порекомендую никому и больше не вернусь</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>негатив</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>сервис</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>нет</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>нет возврата</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>мягкая</t>
+        </is>
+      </c>
+      <c r="J5" t="inlineStr">
+        <is>
+          <t>Негатив</t>
+        </is>
+      </c>
+      <c r="K5" t="inlineStr">
+        <is>
+          <t>Сервис</t>
+        </is>
+      </c>
+      <c r="L5" t="inlineStr">
+        <is>
+          <t>Медленная</t>
+        </is>
+      </c>
+      <c r="M5" t="inlineStr">
+        <is>
+          <t>Нет возврата</t>
+        </is>
+      </c>
+      <c r="N5" t="inlineStr">
+        <is>
+          <t>Корпусная</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>2023</v>
+        <v>8633</v>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t xml:space="preserve">Сарма </t>
+          <t>Эталон</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>1.0</t>
+          <t>5.0</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>К качеству товара претензий нет, но крайне возмутила работа салона! Во-первых, сначала обманули при оформлении заказа - случайно посчитали не тот матрас, естественно дороже 🤷🏻‍♀️ будьте внимательнее при оплате. Во-вторых, не предупредив меня самостоятельно перенесли доставку на другой день. В-третьих, сотрудник Наталья выдумывает разговоры и принимает решения за клиента. Обещали привезти кровать и матрас в один день, в итоге привезли одну кровать, а матрас, как утверждают сотрудники, я сказала заказать на производство 🙄 В-четвёртых, не предупреждают о том, что подъем платный, стоимость подъема из уст сотрудников разнится. Офис говорит 300р, одни грузчики 400, а вторые- 240 🤷🏻‍♀️ Надежда пыталась урегулировать ситуацию и компенсировала расходы на повторную доставку. В общем, я очень расстроена и даже зла на этот офис. Не порекомендую никому и больше не вернусь</t>
+          <t>Для тех кто при деньгах</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>негатив</t>
+          <t>нейтрально</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>сервис</t>
+          <t>нет</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
@@ -777,22 +821,22 @@
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>мягкая</t>
+          <t>нет</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>Негатив</t>
+          <t>Нейтрально</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
         <is>
-          <t>Сервис</t>
+          <t>Иное</t>
         </is>
       </c>
       <c r="L6" t="inlineStr">
         <is>
-          <t>Медленная</t>
+          <t>Нет</t>
         </is>
       </c>
       <c r="M6" t="inlineStr">
@@ -802,37 +846,37 @@
       </c>
       <c r="N6" t="inlineStr">
         <is>
-          <t>Корпусная</t>
+          <t>Нет</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>8633</v>
+        <v>10661</v>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Эталон</t>
+          <t>Март</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>5.0</t>
+          <t>3 звезды</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>Для тех кто при деньгах</t>
+          <t>Салон мебели. Ассортимент не порадовал.</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>нейтрально</t>
+          <t>негатив</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>нет</t>
+          <t>иное</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
@@ -852,7 +896,7 @@
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>Нейтрально</t>
+          <t>Негатив</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
@@ -878,31 +922,31 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>10661</v>
+        <v>10980</v>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Март</t>
+          <t>Эталон</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>3 звезды</t>
+          <t>5 звезд</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>Салон мебели. Ассортимент не порадовал.</t>
+          <t>На первом и третьем этажах экспозиция Лофт.</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>негатив</t>
+          <t>нейтрально</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>иное</t>
+          <t>нет</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
@@ -922,7 +966,7 @@
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>Негатив</t>
+          <t>Нейтрально</t>
         </is>
       </c>
       <c r="K8" t="inlineStr">
@@ -948,26 +992,26 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>10980</v>
+        <v>935</v>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Эталон</t>
+          <t xml:space="preserve">Askona </t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>5 звезд</t>
+          <t>5.0</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>На первом и третьем этажах экспозиция Лофт.</t>
+          <t>Сегодня получили основание с подъёмом и матрас. Очень довольны, все пришло не просто в сроки, а даже раньше. Хотелось бы отметить менеджера Татьяну Ковецкую за очень профессиональный и очень, очень внимательный подход к клиенту! Сразу чувствуется, что она очень грамотный специалист в своём деле. Также хочется поблагодарить Евгения Ковецкого, все собрано было быстро и главное аккуратно, а это так важно!</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>нейтрально</t>
+          <t>позитив</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
@@ -987,22 +1031,22 @@
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>нет</t>
+          <t>мягкая</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>Нейтрально</t>
+          <t>Позитив</t>
         </is>
       </c>
       <c r="K9" t="inlineStr">
         <is>
-          <t>Иное</t>
+          <t>Нет</t>
         </is>
       </c>
       <c r="L9" t="inlineStr">
         <is>
-          <t>Нет</t>
+          <t>Быстрая</t>
         </is>
       </c>
       <c r="M9" t="inlineStr">
@@ -1012,17 +1056,17 @@
       </c>
       <c r="N9" t="inlineStr">
         <is>
-          <t>Нет</t>
+          <t>Мягкая</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>935</v>
+        <v>7359</v>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t xml:space="preserve">Askona </t>
+          <t xml:space="preserve">21 век </t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
@@ -1032,7 +1076,7 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>Сегодня получили основание с подъёмом и матрас. Очень довольны, все пришло не просто в сроки, а даже раньше. Хотелось бы отметить менеджера Татьяну Ковецкую за очень профессиональный и очень, очень внимательный подход к клиенту! Сразу чувствуется, что она очень грамотный специалист в своём деле. Также хочется поблагодарить Евгения Ковецкого, все собрано было быстро и главное аккуратно, а это так важно!</t>
+          <t>Заказывали с мужем кухню с каменной столешницей . Я в восторге !!! Большое спасибо Инне с Николаем за профессионализм! Мою давнюю мечту воплотили в реальность☺️</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
@@ -1057,7 +1101,7 @@
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>мягкая</t>
+          <t>корпусная</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
@@ -1072,7 +1116,7 @@
       </c>
       <c r="L10" t="inlineStr">
         <is>
-          <t>Быстрая</t>
+          <t>Нет</t>
         </is>
       </c>
       <c r="M10" t="inlineStr">
@@ -1082,17 +1126,17 @@
       </c>
       <c r="N10" t="inlineStr">
         <is>
-          <t>Мягкая</t>
+          <t>Корпусная</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>7359</v>
+        <v>3902</v>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t xml:space="preserve">21 век </t>
+          <t xml:space="preserve">МебельСтиль </t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
@@ -1102,7 +1146,7 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>Заказывали с мужем кухню с каменной столешницей . Я в восторге !!! Большое спасибо Инне с Николаем за профессионализм! Мою давнюю мечту воплотили в реальность☺️</t>
+          <t>Сегодня заходил к вам, искал что-то особенное для рабочего места. И нашел классные кресла. Уже у меня дома! Мне нравится</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
@@ -1127,7 +1171,7 @@
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>корпусная</t>
+          <t>нет</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
@@ -1158,11 +1202,11 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>3902</v>
+        <v>4327</v>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t xml:space="preserve">МебельСтиль </t>
+          <t xml:space="preserve">Мебелевич </t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
@@ -1172,7 +1216,8 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>Сегодня заходил к вам, искал что-то особенное для рабочего места. И нашел классные кресла. Уже у меня дома! Мне нравится</t>
+          <t>Сегодня нам установили кухню. Ура!!! Хочу выразить огромную благодарность сборщикам Андрею и Юрию. Сделали всё очень аккуратно и быстро.
+Большое Вам спасибо!</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
@@ -1197,7 +1242,7 @@
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>нет</t>
+          <t>корпусная</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
@@ -1228,32 +1273,31 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>4327</v>
+        <v>8371</v>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t xml:space="preserve">Мебелевич </t>
+          <t>Много Мебели</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>5.0</t>
+          <t>2.0</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>Сегодня нам установили кухню. Ура!!! Хочу выразить огромную благодарность сборщикам Андрею и Юрию. Сделали всё очень аккуратно и быстро.
-Большое Вам спасибо!</t>
+          <t>Не большой выбор мебели, очень навязчивые продавцы.</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>позитив</t>
+          <t>негатив</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>нет</t>
+          <t>сервис</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
@@ -1268,17 +1312,17 @@
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>корпусная</t>
+          <t>нет</t>
         </is>
       </c>
       <c r="J13" t="inlineStr">
         <is>
-          <t>Позитив</t>
+          <t>Негатив</t>
         </is>
       </c>
       <c r="K13" t="inlineStr">
         <is>
-          <t>Нет</t>
+          <t>Сервис</t>
         </is>
       </c>
       <c r="L13" t="inlineStr">
@@ -1293,37 +1337,37 @@
       </c>
       <c r="N13" t="inlineStr">
         <is>
-          <t>Корпусная</t>
+          <t>Нет</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>8371</v>
+        <v>433</v>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Много Мебели</t>
+          <t xml:space="preserve">Ультра </t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>2.0</t>
+          <t>5.0</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>Не большой выбор мебели, очень навязчивые продавцы.</t>
+          <t>Заказала у них комод. Понравилось, что есть возможность выбрать оттенок древесины. Очень стильно и по цене нормально</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>негатив</t>
+          <t>позитив</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>сервис</t>
+          <t>нет</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
@@ -1338,17 +1382,17 @@
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>нет</t>
+          <t>корпусная</t>
         </is>
       </c>
       <c r="J14" t="inlineStr">
         <is>
-          <t>Негатив</t>
+          <t>Позитив</t>
         </is>
       </c>
       <c r="K14" t="inlineStr">
         <is>
-          <t>Сервис</t>
+          <t>Нет</t>
         </is>
       </c>
       <c r="L14" t="inlineStr">
@@ -1363,37 +1407,37 @@
       </c>
       <c r="N14" t="inlineStr">
         <is>
-          <t>Нет</t>
+          <t>Корпусная</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>433</v>
+        <v>1507</v>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t xml:space="preserve">Ультра </t>
+          <t xml:space="preserve">Стол&amp;стул 38 </t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>5.0</t>
+          <t>1.0</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>Заказала у них комод. Понравилось, что есть возможность выбрать оттенок древесины. Очень стильно и по цене нормально</t>
+          <t>Купили в этом магазине раздвижной стол на кухню. Через 2 месяца использования у стола разбухала кромка. В магазине ответили, что это не является производственным браком т.к. туда попала влага. Как использовать кухонный стол, чтобы на него не попадала влага при покупке не объясняют.. замечу, что стол использовался в максимально щадящем режиме, водой ни кто его не поливал. По факту ввели в заблуждение не предупредив, что стол нельзя использовать, как обеденный. По итогу зря потраченные деньги, лучше доплатить и купить более качественную мебель.</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>позитив</t>
+          <t>негатив</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>нет</t>
+          <t>качество</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
@@ -1408,17 +1452,17 @@
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>корпусная</t>
+          <t>нет</t>
         </is>
       </c>
       <c r="J15" t="inlineStr">
         <is>
-          <t>Позитив</t>
+          <t>Негатив</t>
         </is>
       </c>
       <c r="K15" t="inlineStr">
         <is>
-          <t>Нет</t>
+          <t>Качество</t>
         </is>
       </c>
       <c r="L15" t="inlineStr">
@@ -1428,7 +1472,7 @@
       </c>
       <c r="M15" t="inlineStr">
         <is>
-          <t>Нет возврата</t>
+          <t>Другое</t>
         </is>
       </c>
       <c r="N15" t="inlineStr">
@@ -1439,31 +1483,27 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>1507</v>
+        <v>12138</v>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t xml:space="preserve">Стол&amp;стул 38 </t>
+          <t>Мебель Холл</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>1.0</t>
-        </is>
-      </c>
-      <c r="D16" t="inlineStr">
-        <is>
-          <t>Купили в этом магазине раздвижной стол на кухню. Через 2 месяца использования у стола разбухала кромка. В магазине ответили, что это не является производственным браком т.к. туда попала влага. Как использовать кухонный стол, чтобы на него не попадала влага при покупке не объясняют.. замечу, что стол использовался в максимально щадящем режиме, водой ни кто его не поливал. По факту ввели в заблуждение не предупредив, что стол нельзя использовать, как обеденный. По итогу зря потраченные деньги, лучше доплатить и купить более качественную мебель.</t>
-        </is>
-      </c>
+          <t>4 звезды</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr"/>
       <c r="E16" t="inlineStr">
         <is>
-          <t>негатив</t>
+          <t>нейтрально</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>качество</t>
+          <t>нет</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
@@ -1481,50 +1521,34 @@
           <t>нет</t>
         </is>
       </c>
-      <c r="J16" t="inlineStr">
-        <is>
-          <t>Негатив</t>
-        </is>
-      </c>
-      <c r="K16" t="inlineStr">
-        <is>
-          <t>Качество</t>
-        </is>
-      </c>
-      <c r="L16" t="inlineStr">
-        <is>
-          <t>Нет</t>
-        </is>
-      </c>
-      <c r="M16" t="inlineStr">
-        <is>
-          <t>Другое</t>
-        </is>
-      </c>
-      <c r="N16" t="inlineStr">
-        <is>
-          <t>Корпусная</t>
-        </is>
-      </c>
+      <c r="J16" t="inlineStr"/>
+      <c r="K16" t="inlineStr"/>
+      <c r="L16" t="inlineStr"/>
+      <c r="M16" t="inlineStr"/>
+      <c r="N16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>12138</v>
+        <v>10000</v>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Мебель Холл</t>
+          <t>Домашний</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>4 звезды</t>
-        </is>
-      </c>
-      <c r="D17" t="inlineStr"/>
+          <t>5.0</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>Хороший торговый центр с мебелью и сантехникой</t>
+        </is>
+      </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>нейтрально</t>
+          <t>позитив</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
@@ -1547,34 +1571,54 @@
           <t>нет</t>
         </is>
       </c>
-      <c r="J17" t="inlineStr"/>
-      <c r="K17" t="inlineStr"/>
-      <c r="L17" t="inlineStr"/>
-      <c r="M17" t="inlineStr"/>
-      <c r="N17" t="inlineStr"/>
+      <c r="J17" t="inlineStr">
+        <is>
+          <t>Позитив</t>
+        </is>
+      </c>
+      <c r="K17" t="inlineStr">
+        <is>
+          <t>Нет</t>
+        </is>
+      </c>
+      <c r="L17" t="inlineStr">
+        <is>
+          <t>Нет</t>
+        </is>
+      </c>
+      <c r="M17" t="inlineStr">
+        <is>
+          <t>Нет возврата</t>
+        </is>
+      </c>
+      <c r="N17" t="inlineStr">
+        <is>
+          <t>Нет</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>10000</v>
+        <v>305</v>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>Домашний</t>
+          <t xml:space="preserve">Столплит </t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>5.0</t>
+          <t>3.0</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>Хороший торговый центр с мебелью и сантехникой</t>
+          <t>При поставки кухни не хватало фасада, ждали долго когда довезут</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>позитив</t>
+          <t>негатив</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
@@ -1584,7 +1628,7 @@
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>нет</t>
+          <t>медленная</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
@@ -1594,22 +1638,22 @@
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>нет</t>
+          <t>корпусная</t>
         </is>
       </c>
       <c r="J18" t="inlineStr">
         <is>
-          <t>Позитив</t>
+          <t>Негатив</t>
         </is>
       </c>
       <c r="K18" t="inlineStr">
         <is>
-          <t>Нет</t>
+          <t>Сервис</t>
         </is>
       </c>
       <c r="L18" t="inlineStr">
         <is>
-          <t>Нет</t>
+          <t>Медленная</t>
         </is>
       </c>
       <c r="M18" t="inlineStr">
@@ -1619,54 +1663,102 @@
       </c>
       <c r="N18" t="inlineStr">
         <is>
-          <t>Нет</t>
+          <t>Корпусная</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>10409</v>
+        <v>9308</v>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>La soffa</t>
-        </is>
-      </c>
-      <c r="C19" t="inlineStr"/>
-      <c r="D19" t="inlineStr"/>
-      <c r="E19" t="inlineStr"/>
-      <c r="F19" t="inlineStr"/>
-      <c r="G19" t="inlineStr"/>
-      <c r="H19" t="inlineStr"/>
-      <c r="I19" t="inlineStr"/>
-      <c r="J19" t="inlineStr"/>
-      <c r="K19" t="inlineStr"/>
-      <c r="L19" t="inlineStr"/>
-      <c r="M19" t="inlineStr"/>
-      <c r="N19" t="inlineStr"/>
+          <t>Davita-мебель</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>5.0</t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>Бомба, консультанты и очень большие скидки! Заехал с женой потому что делал ремонт, все было очень дешево и очень большой ассортимент. Добрые продавцы и консультанты лично говорят о своем опыте и показывают наилучшую мебель. Также прошу заметить гарантию, примерно в 8 лет, а также скоростную доставку. Мебель пришла буквально через неделю. Еще очень крутой авторский дизайн. Заслуженные 5 звезд 👍.</t>
+        </is>
+      </c>
+      <c r="E19" t="inlineStr">
+        <is>
+          <t>позитив</t>
+        </is>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>нет</t>
+        </is>
+      </c>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>быстрая</t>
+        </is>
+      </c>
+      <c r="H19" t="inlineStr">
+        <is>
+          <t>нет возврата</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr">
+        <is>
+          <t>нет</t>
+        </is>
+      </c>
+      <c r="J19" t="inlineStr">
+        <is>
+          <t>Позитив</t>
+        </is>
+      </c>
+      <c r="K19" t="inlineStr">
+        <is>
+          <t>Нет</t>
+        </is>
+      </c>
+      <c r="L19" t="inlineStr">
+        <is>
+          <t>Быстрая</t>
+        </is>
+      </c>
+      <c r="M19" t="inlineStr">
+        <is>
+          <t>Нет возврата</t>
+        </is>
+      </c>
+      <c r="N19" t="inlineStr">
+        <is>
+          <t>Нет</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>305</v>
+        <v>3087</v>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t xml:space="preserve">Столплит </t>
+          <t xml:space="preserve">Ультра </t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>3.0</t>
+          <t>5.0</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>При поставки кухни не хватало фасада, ждали долго когда довезут</t>
+          <t>Отличный выбор детской мебели в салоне. Нам нужна была кроватка и комод для нашего малыша, и мы нашли идеальные варианты. Дизайн и функциональность на высшем уровне.</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>негатив</t>
+          <t>позитив</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
@@ -1676,7 +1768,7 @@
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>медленная</t>
+          <t>нет</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
@@ -1691,17 +1783,17 @@
       </c>
       <c r="J20" t="inlineStr">
         <is>
-          <t>Негатив</t>
+          <t>Позитив</t>
         </is>
       </c>
       <c r="K20" t="inlineStr">
         <is>
-          <t>Сервис</t>
+          <t>Нет</t>
         </is>
       </c>
       <c r="L20" t="inlineStr">
         <is>
-          <t>Медленная</t>
+          <t>Нет</t>
         </is>
       </c>
       <c r="M20" t="inlineStr">
@@ -1717,66 +1809,67 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>9308</v>
+        <v>5480</v>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>Davita-мебель</t>
+          <t xml:space="preserve">Divan Boss </t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>5.0</t>
+          <t>1.0</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>Бомба, консультанты и очень большие скидки! Заехал с женой потому что делал ремонт, все было очень дешево и очень большой ассортимент. Добрые продавцы и консультанты лично говорят о своем опыте и показывают наилучшую мебель. Также прошу заметить гарантию, примерно в 8 лет, а также скоростную доставку. Мебель пришла буквально через неделю. Еще очень крутой авторский дизайн. Заслуженные 5 звезд 👍.</t>
+          <t>Обходите эти салоны стороной!!! Заказали мебель и сборку 16 июня 2023 г . - по габаритам не подошла . Через 3 дня написали заявление на возврат денежных средств 19 июня 2023 г Администратор бросает трубки , деньги до сих пор не вернули. Видимо свои же деньги нужно будет забирать через суд.
+Информирую вас о том , что если деньги не поступят на счёт до 4 июля 2023 года , будет направлено заявление в Роспотребнадзор о факте мошенничества и нарушении прав потребителей , а также исковое заявление о факте мошенничества и нарушении прав потребителей и незаконном присвоении и использовании чужих денежных средств будет направлено в судебные органы.</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>позитив</t>
+          <t>негатив</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>нет</t>
+          <t>иное</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>быстрая</t>
+          <t>нет</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>нет возврата</t>
+          <t>другое</t>
         </is>
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>нет</t>
+          <t>корпусная</t>
         </is>
       </c>
       <c r="J21" t="inlineStr">
         <is>
-          <t>Позитив</t>
+          <t>Негатив</t>
         </is>
       </c>
       <c r="K21" t="inlineStr">
         <is>
-          <t>Нет</t>
+          <t>Сервис</t>
         </is>
       </c>
       <c r="L21" t="inlineStr">
         <is>
-          <t>Быстрая</t>
+          <t>Нет</t>
         </is>
       </c>
       <c r="M21" t="inlineStr">
         <is>
-          <t>Нет возврата</t>
+          <t>Несоответствие описанию</t>
         </is>
       </c>
       <c r="N21" t="inlineStr">
@@ -1787,11 +1880,11 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>3087</v>
+        <v>1658</v>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t xml:space="preserve">Ультра </t>
+          <t xml:space="preserve">МЕБЕЛЬНЫЙ ДВОР </t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
@@ -1801,7 +1894,7 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>Отличный выбор детской мебели в салоне. Нам нужна была кроватка и комод для нашего малыша, и мы нашли идеальные варианты. Дизайн и функциональность на высшем уровне.</t>
+          <t>Здесь я купила шкаф, который уже давно запал мне в душу! Полностью устроило соотношение «цена-качество»! Быстро оформили покупку, организовали доставку, согласовали время сборки. Всё выполнено в срок! Руками профессионального сборщика шкаф был собран минут за 40!!! Благодарна за качественный сервис! Рекомендую!!!</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
@@ -1816,7 +1909,7 @@
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>нет</t>
+          <t>быстрая</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
@@ -1841,7 +1934,7 @@
       </c>
       <c r="L22" t="inlineStr">
         <is>
-          <t>Нет</t>
+          <t>Быстрая</t>
         </is>
       </c>
       <c r="M22" t="inlineStr">
@@ -1857,11 +1950,11 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>5480</v>
+        <v>1305</v>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t xml:space="preserve">Divan Boss </t>
+          <t xml:space="preserve">Сарма </t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
@@ -1871,8 +1964,7 @@
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>Обходите эти салоны стороной!!! Заказали мебель и сборку 16 июня 2023 г . - по габаритам не подошла . Через 3 дня написали заявление на возврат денежных средств 19 июня 2023 г Администратор бросает трубки , деньги до сих пор не вернули. Видимо свои же деньги нужно будет забирать через суд.
-Информирую вас о том , что если деньги не поступят на счёт до 4 июля 2023 года , будет направлено заявление в Роспотребнадзор о факте мошенничества и нарушении прав потребителей , а также исковое заявление о факте мошенничества и нарушении прав потребителей и незаконном присвоении и использовании чужих денежных средств будет направлено в судебные органы.</t>
+          <t>Была в вашем магазине 12.06.20 в тц акцент, работала консультант Евгения. Так как я очень долго мучалась с выбором подушки, много информации прочла по тому, как нужно ее выбирать и по тому как консультант должен помогать в выборе (хотя бы поинтересоваться в какой позе привык спать человек) я уточнила этот момент у Евгении, сообщив о том, что возможно подушка, какую она мне предложила изначально, немного низковата исходя из моих сведений о выборе. Говорила я спокойно, безо всякого желания «конфликтовать». На что Евгения ответила мне «если я пришла права качать, то мне не сюда». На что я просто развернулась и купила подушку в Асконе) Уважаемое руководство, вы уж перед Евгенией извинитесь, раз «рядовой» покупатель такими вопросами «права качает» и объясните, что сотрудники сферы услуг, не должны так разговоривать ни потому что находятся на работе, ни потому что это в принципе невоспитанно, если у вас есть приоритет на покупателя. Спасибо)</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
@@ -1882,7 +1974,7 @@
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>иное</t>
+          <t>сервис</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
@@ -1892,12 +1984,12 @@
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>другое</t>
+          <t>нет возврата</t>
         </is>
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t>корпусная</t>
+          <t>нет</t>
         </is>
       </c>
       <c r="J23" t="inlineStr">
@@ -1917,22 +2009,22 @@
       </c>
       <c r="M23" t="inlineStr">
         <is>
-          <t>Несоответствие описанию</t>
+          <t>Нет возврата</t>
         </is>
       </c>
       <c r="N23" t="inlineStr">
         <is>
-          <t>Нет</t>
+          <t>Мягкая</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>1658</v>
+        <v>9836</v>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t xml:space="preserve">МЕБЕЛЬНЫЙ ДВОР </t>
+          <t>DaVita</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
@@ -1942,7 +2034,7 @@
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>Здесь я купила шкаф, который уже давно запал мне в душу! Полностью устроило соотношение «цена-качество»! Быстро оформили покупку, организовали доставку, согласовали время сборки. Всё выполнено в срок! Руками профессионального сборщика шкаф был собран минут за 40!!! Благодарна за качественный сервис! Рекомендую!!!</t>
+          <t>Выражаю огромную благодарность менеджеру Анастасии за профессионализм, понимание и терпение! Благодаря ей теперь любуемся новой кухней! Ну а качество мебели отдельный восторг! Очень-очень довольны!</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
@@ -1957,7 +2049,7 @@
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>быстрая</t>
+          <t>нет</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
@@ -1982,7 +2074,7 @@
       </c>
       <c r="L24" t="inlineStr">
         <is>
-          <t>Быстрая</t>
+          <t>Нет</t>
         </is>
       </c>
       <c r="M24" t="inlineStr">
@@ -1998,31 +2090,31 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>1305</v>
+        <v>11474</v>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t xml:space="preserve">Сарма </t>
+          <t>Адель</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>1.0</t>
+          <t>3 звезды</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>Была в вашем магазине 12.06.20 в тц акцент, работала консультант Евгения. Так как я очень долго мучалась с выбором подушки, много информации прочла по тому, как нужно ее выбирать и по тому как консультант должен помогать в выборе (хотя бы поинтересоваться в какой позе привык спать человек) я уточнила этот момент у Евгении, сообщив о том, что возможно подушка, какую она мне предложила изначально, немного низковата исходя из моих сведений о выборе. Говорила я спокойно, безо всякого желания «конфликтовать». На что Евгения ответила мне «если я пришла права качать, то мне не сюда». На что я просто развернулась и купила подушку в Асконе) Уважаемое руководство, вы уж перед Евгенией извинитесь, раз «рядовой» покупатель такими вопросами «права качает» и объясните, что сотрудники сферы услуг, не должны так разговоривать ни потому что находятся на работе, ни потому что это в принципе невоспитанно, если у вас есть приоритет на покупателя. Спасибо)</t>
+          <t>Не был не знаю</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>негатив</t>
+          <t>нейтрально</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>сервис</t>
+          <t>нет</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
@@ -2042,12 +2134,12 @@
       </c>
       <c r="J25" t="inlineStr">
         <is>
-          <t>Негатив</t>
+          <t>Нейтрально</t>
         </is>
       </c>
       <c r="K25" t="inlineStr">
         <is>
-          <t>Сервис</t>
+          <t>Нет</t>
         </is>
       </c>
       <c r="L25" t="inlineStr">
@@ -2062,17 +2154,17 @@
       </c>
       <c r="N25" t="inlineStr">
         <is>
-          <t>Мягкая</t>
+          <t>Нет</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>9836</v>
+        <v>4504</v>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>DaVita</t>
+          <t xml:space="preserve">Мебелевич </t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
@@ -2081,146 +2173,6 @@
         </is>
       </c>
       <c r="D26" t="inlineStr">
-        <is>
-          <t>Выражаю огромную благодарность менеджеру Анастасии за профессионализм, понимание и терпение! Благодаря ей теперь любуемся новой кухней! Ну а качество мебели отдельный восторг! Очень-очень довольны!</t>
-        </is>
-      </c>
-      <c r="E26" t="inlineStr">
-        <is>
-          <t>позитив</t>
-        </is>
-      </c>
-      <c r="F26" t="inlineStr">
-        <is>
-          <t>нет</t>
-        </is>
-      </c>
-      <c r="G26" t="inlineStr">
-        <is>
-          <t>нет</t>
-        </is>
-      </c>
-      <c r="H26" t="inlineStr">
-        <is>
-          <t>нет возврата</t>
-        </is>
-      </c>
-      <c r="I26" t="inlineStr">
-        <is>
-          <t>корпусная</t>
-        </is>
-      </c>
-      <c r="J26" t="inlineStr">
-        <is>
-          <t>Позитив</t>
-        </is>
-      </c>
-      <c r="K26" t="inlineStr">
-        <is>
-          <t>Нет</t>
-        </is>
-      </c>
-      <c r="L26" t="inlineStr">
-        <is>
-          <t>Нет</t>
-        </is>
-      </c>
-      <c r="M26" t="inlineStr">
-        <is>
-          <t>Нет возврата</t>
-        </is>
-      </c>
-      <c r="N26" t="inlineStr">
-        <is>
-          <t>Корпусная</t>
-        </is>
-      </c>
-    </row>
-    <row r="27">
-      <c r="A27" t="n">
-        <v>11474</v>
-      </c>
-      <c r="B27" t="inlineStr">
-        <is>
-          <t>Адель</t>
-        </is>
-      </c>
-      <c r="C27" t="inlineStr">
-        <is>
-          <t>3 звезды</t>
-        </is>
-      </c>
-      <c r="D27" t="inlineStr">
-        <is>
-          <t>Не был не знаю</t>
-        </is>
-      </c>
-      <c r="E27" t="inlineStr">
-        <is>
-          <t>нейтрально</t>
-        </is>
-      </c>
-      <c r="F27" t="inlineStr">
-        <is>
-          <t>нет</t>
-        </is>
-      </c>
-      <c r="G27" t="inlineStr">
-        <is>
-          <t>нет</t>
-        </is>
-      </c>
-      <c r="H27" t="inlineStr">
-        <is>
-          <t>нет возврата</t>
-        </is>
-      </c>
-      <c r="I27" t="inlineStr">
-        <is>
-          <t>нет</t>
-        </is>
-      </c>
-      <c r="J27" t="inlineStr">
-        <is>
-          <t>Нейтрально</t>
-        </is>
-      </c>
-      <c r="K27" t="inlineStr">
-        <is>
-          <t>Нет</t>
-        </is>
-      </c>
-      <c r="L27" t="inlineStr">
-        <is>
-          <t>Нет</t>
-        </is>
-      </c>
-      <c r="M27" t="inlineStr">
-        <is>
-          <t>Нет возврата</t>
-        </is>
-      </c>
-      <c r="N27" t="inlineStr">
-        <is>
-          <t>Нет</t>
-        </is>
-      </c>
-    </row>
-    <row r="28">
-      <c r="A28" t="n">
-        <v>4504</v>
-      </c>
-      <c r="B28" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Мебелевич </t>
-        </is>
-      </c>
-      <c r="C28" t="inlineStr">
-        <is>
-          <t>5.0</t>
-        </is>
-      </c>
-      <c r="D28" t="inlineStr">
         <is>
           <t>Заказываем тут не в первый раз, всегда всё легко и просто. Очень довольны сотрудниками и качеством исполнения!
 Менеджер Елена всё подробно объясняет и предлагает варианты, всегда вежлива и учитывает все особенности мебели!
@@ -2229,6 +2181,146 @@
 Рекомендую всем и буду заказывать здесь ещё :)</t>
         </is>
       </c>
+      <c r="E26" t="inlineStr">
+        <is>
+          <t>позитив</t>
+        </is>
+      </c>
+      <c r="F26" t="inlineStr">
+        <is>
+          <t>нет</t>
+        </is>
+      </c>
+      <c r="G26" t="inlineStr">
+        <is>
+          <t>нет</t>
+        </is>
+      </c>
+      <c r="H26" t="inlineStr">
+        <is>
+          <t>нет возврата</t>
+        </is>
+      </c>
+      <c r="I26" t="inlineStr">
+        <is>
+          <t>нет</t>
+        </is>
+      </c>
+      <c r="J26" t="inlineStr">
+        <is>
+          <t>Позитив</t>
+        </is>
+      </c>
+      <c r="K26" t="inlineStr">
+        <is>
+          <t>Нет</t>
+        </is>
+      </c>
+      <c r="L26" t="inlineStr">
+        <is>
+          <t>Нет</t>
+        </is>
+      </c>
+      <c r="M26" t="inlineStr">
+        <is>
+          <t>Нет возврата</t>
+        </is>
+      </c>
+      <c r="N26" t="inlineStr">
+        <is>
+          <t>Нет</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="n">
+        <v>8979</v>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>Мир мебели</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>5.0</t>
+        </is>
+      </c>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>Купили красивую и функциональную кровать Регата. Ребенку очень понравилась.</t>
+        </is>
+      </c>
+      <c r="E27" t="inlineStr">
+        <is>
+          <t>позитив</t>
+        </is>
+      </c>
+      <c r="F27" t="inlineStr">
+        <is>
+          <t>нет</t>
+        </is>
+      </c>
+      <c r="G27" t="inlineStr">
+        <is>
+          <t>нет</t>
+        </is>
+      </c>
+      <c r="H27" t="inlineStr">
+        <is>
+          <t>нет возврата</t>
+        </is>
+      </c>
+      <c r="I27" t="inlineStr">
+        <is>
+          <t>корпусная</t>
+        </is>
+      </c>
+      <c r="J27" t="inlineStr">
+        <is>
+          <t>Позитив</t>
+        </is>
+      </c>
+      <c r="K27" t="inlineStr">
+        <is>
+          <t>Нет</t>
+        </is>
+      </c>
+      <c r="L27" t="inlineStr">
+        <is>
+          <t>Нет</t>
+        </is>
+      </c>
+      <c r="M27" t="inlineStr">
+        <is>
+          <t>Нет возврата</t>
+        </is>
+      </c>
+      <c r="N27" t="inlineStr">
+        <is>
+          <t>Корпусная</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="n">
+        <v>227</v>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Столплит </t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>5.0</t>
+        </is>
+      </c>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>Приобрел отличную мебель, которая не подвела меня ни своим качеством, ни ценой. Выражаю благодарность Татьяне Михайловне за такой широкий выбор и качество товара.</t>
+        </is>
+      </c>
       <c r="E28" t="inlineStr">
         <is>
           <t>позитив</t>
@@ -2282,11 +2374,11 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>8979</v>
+        <v>5027</v>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>Мир мебели</t>
+          <t xml:space="preserve">Бартер </t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
@@ -2296,7 +2388,7 @@
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>Купили красивую и функциональную кровать Регата. Ребенку очень понравилась.</t>
+          <t>Магазин нравится. Отличный, вежливый персонал. Хороший выбор товаров.</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
@@ -2321,7 +2413,7 @@
       </c>
       <c r="I29" t="inlineStr">
         <is>
-          <t>корпусная</t>
+          <t>нет</t>
         </is>
       </c>
       <c r="J29" t="inlineStr">
@@ -2346,17 +2438,17 @@
       </c>
       <c r="N29" t="inlineStr">
         <is>
-          <t>Корпусная</t>
+          <t>Нет</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>227</v>
+        <v>1597</v>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t xml:space="preserve">Столплит </t>
+          <t xml:space="preserve">Sib-Stone </t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
@@ -2366,7 +2458,7 @@
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>Приобрел отличную мебель, которая не подвела меня ни своим качеством, ни ценой. Выражаю благодарность Татьяне Михайловне за такой широкий выбор и качество товара.</t>
+          <t>Хочу выразить огромную благодарность профессионалам своего дела! Все отлично сделали, даже раньше установленного срока! Заказываем не первый раз, всегда все четко! Первые столешницы уже проверены временем, 5 лет использования -в идеальном состоянии! С полной уверенностью РЕКОМЕНДУЮ!</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
@@ -2381,7 +2473,7 @@
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>нет</t>
+          <t>быстрая</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
@@ -2406,7 +2498,7 @@
       </c>
       <c r="L30" t="inlineStr">
         <is>
-          <t>Нет</t>
+          <t>Быстрая</t>
         </is>
       </c>
       <c r="M30" t="inlineStr">
@@ -2416,17 +2508,17 @@
       </c>
       <c r="N30" t="inlineStr">
         <is>
-          <t>Нет</t>
+          <t>Корпусная</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>5027</v>
+        <v>6052</v>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t xml:space="preserve">Бартер </t>
+          <t xml:space="preserve">Fantasy </t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
@@ -2436,7 +2528,7 @@
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>Магазин нравится. Отличный, вежливый персонал. Хороший выбор товаров.</t>
+          <t>Хотим сказать большое спасибо компании Fantasy) вся мебель в нашей квартире производства этой компании: кухонный гарнитур, детские, гардеробные, зеркало в ванную, тумба в ванную под раковину, шкаф в коридоре) качество отличное) менеджер Виктория учла предпочтения каждого члена семьи и помогла создать уникальное, продуманное до мелочей, собственное пространство для каждого) отдельное спасибо ребятам, которые собирали мебель, все профессионалы👍 последнее приобретение нашей семьи в этой компании это диван) качество 💥, раскладывается в полноценную кровать! Виктория идеально подобрала его в наш интерьер! Большое спасибо компании Fanfasy ❤️❤️❤️</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
@@ -2461,7 +2553,7 @@
       </c>
       <c r="I31" t="inlineStr">
         <is>
-          <t>нет</t>
+          <t>корпусная</t>
         </is>
       </c>
       <c r="J31" t="inlineStr">
@@ -2486,17 +2578,17 @@
       </c>
       <c r="N31" t="inlineStr">
         <is>
-          <t>Нет</t>
+          <t>Корпусная</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>1597</v>
+        <v>9039</v>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t xml:space="preserve">Sib-Stone </t>
+          <t>Мир мебели</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
@@ -2506,7 +2598,7 @@
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>Хочу выразить огромную благодарность профессионалам своего дела! Все отлично сделали, даже раньше установленного срока! Заказываем не первый раз, всегда все четко! Первые столешницы уже проверены временем, 5 лет использования -в идеальном состоянии! С полной уверенностью РЕКОМЕНДУЮ!</t>
+          <t>покупала обеденную группу. Качество отличное. Стол легко раскладывается, покрытие идеальное. Никаких царапин, сколов, трещин. Стулья очень удобные и устойчивые. В целом все отлично. Порадовали.</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
@@ -2521,7 +2613,7 @@
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>быстрая</t>
+          <t>нет</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
@@ -2546,7 +2638,7 @@
       </c>
       <c r="L32" t="inlineStr">
         <is>
-          <t>Быстрая</t>
+          <t>Нет</t>
         </is>
       </c>
       <c r="M32" t="inlineStr">
@@ -2562,11 +2654,11 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>6052</v>
+        <v>8842</v>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t xml:space="preserve">Fantasy </t>
+          <t>Планета Мебели</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
@@ -2576,7 +2668,7 @@
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>Хотим сказать большое спасибо компании Fantasy) вся мебель в нашей квартире производства этой компании: кухонный гарнитур, детские, гардеробные, зеркало в ванную, тумба в ванную под раковину, шкаф в коридоре) качество отличное) менеджер Виктория учла предпочтения каждого члена семьи и помогла создать уникальное, продуманное до мелочей, собственное пространство для каждого) отдельное спасибо ребятам, которые собирали мебель, все профессионалы👍 последнее приобретение нашей семьи в этой компании это диван) качество 💥, раскладывается в полноценную кровать! Виктория идеально подобрала его в наш интерьер! Большое спасибо компании Fanfasy ❤️❤️❤️</t>
+          <t>Низкие цены, имеется рассрочка при которой мебель забираете сразу, что не мало важно при наших зарплатах. Вежливый персонал, спасибо девочкам. Рекомендуею всем.</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
@@ -2601,7 +2693,7 @@
       </c>
       <c r="I33" t="inlineStr">
         <is>
-          <t>корпусная</t>
+          <t>нет</t>
         </is>
       </c>
       <c r="J33" t="inlineStr">
@@ -2626,13 +2718,13 @@
       </c>
       <c r="N33" t="inlineStr">
         <is>
-          <t>Корпусная</t>
+          <t>Нет</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>9039</v>
+        <v>9062</v>
       </c>
       <c r="B34" t="inlineStr">
         <is>
@@ -2646,7 +2738,7 @@
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>покупала обеденную группу. Качество отличное. Стол легко раскладывается, покрытие идеальное. Никаких царапин, сколов, трещин. Стулья очень удобные и устойчивые. В целом все отлично. Порадовали.</t>
+          <t>Хорошая мебель от многих производителей. Доставка, сборка. Рекомендую.</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
@@ -2661,7 +2753,7 @@
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>нет</t>
+          <t>быстрая</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
@@ -2696,17 +2788,17 @@
       </c>
       <c r="N34" t="inlineStr">
         <is>
-          <t>Корпусная</t>
+          <t>Нет</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>8842</v>
+        <v>1248</v>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>Планета Мебели</t>
+          <t xml:space="preserve">Askona </t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
@@ -2716,7 +2808,7 @@
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>Низкие цены, имеется рассрочка при которой мебель забираете сразу, что не мало важно при наших зарплатах. Вежливый персонал, спасибо девочкам. Рекомендуею всем.</t>
+          <t>Благодарим Татьяну и парня Евгения в помощи выбора , грамотную консультацию и поддержку на всех этапах покупки и получения матраса, спасибо за вашу работу и профессионализм ❤</t>
         </is>
       </c>
       <c r="E35" t="inlineStr">
@@ -2766,17 +2858,17 @@
       </c>
       <c r="N35" t="inlineStr">
         <is>
-          <t>Нет</t>
+          <t>Мягкая</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>9062</v>
+        <v>217</v>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>Мир мебели</t>
+          <t xml:space="preserve">Столплит </t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
@@ -2786,7 +2878,7 @@
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>Хорошая мебель от многих производителей. Доставка, сборка. Рекомендую.</t>
+          <t>В этом магазине мне понравился абсолютно весь ассортимент!! Выбирала достаточно долго, потому что аж глаза разбегаются при виде красивой и стильной мебели! Приобрела мебель на кухню и отличный комод, который прекрасно теперь украшает мою комнату!!</t>
         </is>
       </c>
       <c r="E36" t="inlineStr">
@@ -2801,7 +2893,7 @@
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>быстрая</t>
+          <t>нет</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
@@ -2811,7 +2903,7 @@
       </c>
       <c r="I36" t="inlineStr">
         <is>
-          <t>нет</t>
+          <t>корпусная</t>
         </is>
       </c>
       <c r="J36" t="inlineStr">
@@ -2836,17 +2928,17 @@
       </c>
       <c r="N36" t="inlineStr">
         <is>
-          <t>Нет</t>
+          <t>Корпусная</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>1248</v>
+        <v>8646</v>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t xml:space="preserve">Askona </t>
+          <t>Мебельный Двор</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
@@ -2856,7 +2948,7 @@
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>Благодарим Татьяну и парня Евгения в помощи выбора , грамотную консультацию и поддержку на всех этапах покупки и получения матраса, спасибо за вашу работу и профессионализм ❤</t>
+          <t>Всегда большой выбор и цены не очень высокие.В ноябре искала тумбочку под телевизор длиной более метра,обьехала очень много мебельных магазинов,а нашла только в этом магазине(по приемлемой цене).Мебель берем уже не один раз в этой фирме,очень давольны.</t>
         </is>
       </c>
       <c r="E37" t="inlineStr">
@@ -2881,7 +2973,7 @@
       </c>
       <c r="I37" t="inlineStr">
         <is>
-          <t>нет</t>
+          <t>корпусная</t>
         </is>
       </c>
       <c r="J37" t="inlineStr">
@@ -2906,17 +2998,17 @@
       </c>
       <c r="N37" t="inlineStr">
         <is>
-          <t>Мягкая</t>
+          <t>Корпусная</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>217</v>
+        <v>2374</v>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t xml:space="preserve">Столплит </t>
+          <t xml:space="preserve">Tandem comfort </t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
@@ -2926,7 +3018,7 @@
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>В этом магазине мне понравился абсолютно весь ассортимент!! Выбирала достаточно долго, потому что аж глаза разбегаются при виде красивой и стильной мебели! Приобрела мебель на кухню и отличный комод, который прекрасно теперь украшает мою комнату!!</t>
+          <t>купили кровать.очень довольны покупкой,доставка в этот же день, очень приятный консультант)))</t>
         </is>
       </c>
       <c r="E38" t="inlineStr">
@@ -2941,7 +3033,7 @@
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>нет</t>
+          <t>быстрая</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
@@ -2951,7 +3043,7 @@
       </c>
       <c r="I38" t="inlineStr">
         <is>
-          <t>корпусная</t>
+          <t>нет</t>
         </is>
       </c>
       <c r="J38" t="inlineStr">
@@ -2966,7 +3058,7 @@
       </c>
       <c r="L38" t="inlineStr">
         <is>
-          <t>Нет</t>
+          <t>Быстрая</t>
         </is>
       </c>
       <c r="M38" t="inlineStr">
@@ -2982,11 +3074,11 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>8646</v>
+        <v>4880</v>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>Мебельный Двор</t>
+          <t xml:space="preserve">Варвара </t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
@@ -2996,7 +3088,8 @@
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>Всегда большой выбор и цены не очень высокие.В ноябре искала тумбочку под телевизор длиной более метра,обьехала очень много мебельных магазинов,а нашла только в этом магазине(по приемлемой цене).Мебель берем уже не один раз в этой фирме,очень давольны.</t>
+          <t>Хотелось не только красивую кухню, но и функциональную. Чтобы каждый метр использовать рационально. Посоветовались, Александра нам предложила два варианта на выбор, сразу выбрали, это любовь с первого взгляда была 💖
+И по цветовой гамме и по наполнению. Изготовление около 3 недель было, довольно-таки быстро!</t>
         </is>
       </c>
       <c r="E39" t="inlineStr">
@@ -3021,7 +3114,7 @@
       </c>
       <c r="I39" t="inlineStr">
         <is>
-          <t>корпусная</t>
+          <t>нет</t>
         </is>
       </c>
       <c r="J39" t="inlineStr">
@@ -3036,7 +3129,7 @@
       </c>
       <c r="L39" t="inlineStr">
         <is>
-          <t>Нет</t>
+          <t>Быстрая</t>
         </is>
       </c>
       <c r="M39" t="inlineStr">
@@ -3052,26 +3145,26 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>2374</v>
+        <v>12112</v>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t xml:space="preserve">Tandem comfort </t>
+          <t>Мебель Холл</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>5.0</t>
+          <t>4 звезды</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>купили кровать.очень довольны покупкой,доставка в этот же день, очень приятный консультант)))</t>
+          <t>Нормально выбор есть боле менее</t>
         </is>
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>позитив</t>
+          <t>нейтрально</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
@@ -3081,7 +3174,7 @@
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>быстрая</t>
+          <t>нет</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
@@ -3096,7 +3189,7 @@
       </c>
       <c r="J40" t="inlineStr">
         <is>
-          <t>Позитив</t>
+          <t>Нейтрально</t>
         </is>
       </c>
       <c r="K40" t="inlineStr">
@@ -3106,7 +3199,7 @@
       </c>
       <c r="L40" t="inlineStr">
         <is>
-          <t>Быстрая</t>
+          <t>Нет</t>
         </is>
       </c>
       <c r="M40" t="inlineStr">
@@ -3116,17 +3209,17 @@
       </c>
       <c r="N40" t="inlineStr">
         <is>
-          <t>Корпусная</t>
+          <t>Нет</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>4880</v>
+        <v>2346</v>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t xml:space="preserve">Варвара </t>
+          <t xml:space="preserve">Lazurit </t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
@@ -3136,8 +3229,7 @@
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>Хотелось не только красивую кухню, но и функциональную. Чтобы каждый метр использовать рационально. Посоветовались, Александра нам предложила два варианта на выбор, сразу выбрали, это любовь с первого взгляда была 💖
-И по цветовой гамме и по наполнению. Изготовление около 3 недель было, довольно-таки быстро!</t>
+          <t>В конце июля заказывали детскую, вчера наконец-то пришел наш заказ с фабрики. Доставили все в идеальном состоянии. Хочу поблагодарить сборщиков Максима и Сергея, супер-парни! Все сделали быстро, за собой мусор убрали. В следующий раз тоже пойдем в Лазурит.</t>
         </is>
       </c>
       <c r="E41" t="inlineStr">
@@ -3162,7 +3254,7 @@
       </c>
       <c r="I41" t="inlineStr">
         <is>
-          <t>нет</t>
+          <t>корпусная</t>
         </is>
       </c>
       <c r="J41" t="inlineStr">
@@ -3177,7 +3269,7 @@
       </c>
       <c r="L41" t="inlineStr">
         <is>
-          <t>Быстрая</t>
+          <t>Медленная</t>
         </is>
       </c>
       <c r="M41" t="inlineStr">
@@ -3193,26 +3285,26 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>12112</v>
+        <v>7263</v>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>Мебель Холл</t>
+          <t xml:space="preserve">Аврора </t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>4 звезды</t>
+          <t>5.0</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>Нормально выбор есть боле менее</t>
+          <t>Заказали стол, доставили даже раньше на 2 дня, хоть он был по индивидуальным размерам. Выглядит очень стильно и дорого!</t>
         </is>
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>нейтрально</t>
+          <t>позитив</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
@@ -3222,7 +3314,7 @@
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>нет</t>
+          <t>быстрая</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
@@ -3237,7 +3329,7 @@
       </c>
       <c r="J42" t="inlineStr">
         <is>
-          <t>Нейтрально</t>
+          <t>Позитив</t>
         </is>
       </c>
       <c r="K42" t="inlineStr">
@@ -3247,7 +3339,7 @@
       </c>
       <c r="L42" t="inlineStr">
         <is>
-          <t>Нет</t>
+          <t>Быстрая</t>
         </is>
       </c>
       <c r="M42" t="inlineStr">
@@ -3257,17 +3349,17 @@
       </c>
       <c r="N42" t="inlineStr">
         <is>
-          <t>Нет</t>
+          <t>Корпусная</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>2346</v>
+        <v>5415</v>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t xml:space="preserve">Lazurit </t>
+          <t xml:space="preserve">Импровизация </t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
@@ -3277,7 +3369,7 @@
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>В конце июля заказывали детскую, вчера наконец-то пришел наш заказ с фабрики. Доставили все в идеальном состоянии. Хочу поблагодарить сборщиков Максима и Сергея, супер-парни! Все сделали быстро, за собой мусор убрали. В следующий раз тоже пойдем в Лазурит.</t>
+          <t>Здравствуйте!Хотели бы сказать отдельное спасибо мастеру по установке кухонного гарнитура Александру Пискайкину. Такие ответственные мастера своего дела большая редкость, потому что он выполнил свою работу так, как для себя.Очень кропотливо и внимательно произвел всю установку гарнитура и решил вопросы, которые возникли в процессе монтажа (неровные полы, стены и т.д.)...мастер с большим опытом работы выполнил все в лучшем виде. Отдельное спасибо менеджеру Алене, которая также помогла в выборе и решила вопросы по доп. материалам. Работа сервиса данного мебельного салона на высоком уровне, сроки доставки ориентированы на клиента (за что отделье спасибо!!!!), все вопросы решаются мгновенно.Очень рады что остановились на Вашем салоне мебели!Радуемся новой кухне😊Александр, еще раз спасибо!!!Очень рекомендуем данного мастера!!!!!!</t>
         </is>
       </c>
       <c r="E43" t="inlineStr">
@@ -3317,7 +3409,7 @@
       </c>
       <c r="L43" t="inlineStr">
         <is>
-          <t>Медленная</t>
+          <t>Быстрая</t>
         </is>
       </c>
       <c r="M43" t="inlineStr">
@@ -3333,33 +3425,77 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>11581</v>
+        <v>5481</v>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>Адель</t>
+          <t xml:space="preserve">Divan Boss </t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>5 звезд</t>
-        </is>
-      </c>
-      <c r="D44" t="inlineStr"/>
-      <c r="E44" t="inlineStr"/>
-      <c r="F44" t="inlineStr"/>
-      <c r="G44" t="inlineStr"/>
-      <c r="H44" t="inlineStr"/>
-      <c r="I44" t="inlineStr"/>
-      <c r="J44" t="inlineStr"/>
-      <c r="K44" t="inlineStr"/>
-      <c r="L44" t="inlineStr"/>
-      <c r="M44" t="inlineStr"/>
-      <c r="N44" t="inlineStr"/>
+          <t>1.0</t>
+        </is>
+      </c>
+      <c r="D44" t="inlineStr">
+        <is>
+          <t>Читайте отзывы, пожалуйста, прежде чем покупать в салонах и вообще читайте, штудируйте все и везде, прежде чем что-то где-то покупать.сейчас большинство фабрик работают, к сожалению, не на качество!!!Вот мы лоханулись😂….. но блииииин,у нас не возникло никаких сомнений, потому как пошли в салон по рекомендации людей, которые были в восторге от мебели, и мы даже не задумались, что может что-то пойти не так🤪 покупали диван 2 мая, доставка была 25.06, продавец заверяла, что доставка около 3-х недель, ну ладно ждем…. Периодически спрашиваем ,что там по доставке… ждите, диван уже на складе, скоро привезут, ну вот настало ЭТО СКОРО 18 июня🤣пришло сообщение от курьерской службы - диван доставим с такого то часа по такой-то… прошло 18 число, ничего не привезли… никто не предупредил даже что доставка задерживается, ничего не привезем и тд!!!!! Приходит сообщение -ждите доставку 25 июня, позвонили в магазин -точно ли доставка на 25 июня или опять нас так же опрокинут?!?! Столько букв в одно сообщение не вместится, надо выговорится и описать все в подробностях может руководство магазина обратит внимание?!?!?! Или все потеряно окончательно для этого магазина?!?!? ПРОДОЛЖЕНИИ ИСТОРИИ НИЖЕ В КОММЕНТАРИЯХ…⬇️</t>
+        </is>
+      </c>
+      <c r="E44" t="inlineStr">
+        <is>
+          <t>негатив</t>
+        </is>
+      </c>
+      <c r="F44" t="inlineStr">
+        <is>
+          <t>сервис</t>
+        </is>
+      </c>
+      <c r="G44" t="inlineStr">
+        <is>
+          <t>медленная</t>
+        </is>
+      </c>
+      <c r="H44" t="inlineStr">
+        <is>
+          <t>нет возврата</t>
+        </is>
+      </c>
+      <c r="I44" t="inlineStr">
+        <is>
+          <t>мягкая</t>
+        </is>
+      </c>
+      <c r="J44" t="inlineStr">
+        <is>
+          <t>Негатив</t>
+        </is>
+      </c>
+      <c r="K44" t="inlineStr">
+        <is>
+          <t>Сервис</t>
+        </is>
+      </c>
+      <c r="L44" t="inlineStr">
+        <is>
+          <t>Медленная</t>
+        </is>
+      </c>
+      <c r="M44" t="inlineStr">
+        <is>
+          <t>Нет возврата</t>
+        </is>
+      </c>
+      <c r="N44" t="inlineStr">
+        <is>
+          <t>Мягкая</t>
+        </is>
+      </c>
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>7263</v>
+        <v>7260</v>
       </c>
       <c r="B45" t="inlineStr">
         <is>
@@ -3373,7 +3509,7 @@
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>Заказали стол, доставили даже раньше на 2 дня, хоть он был по индивидуальным размерам. Выглядит очень стильно и дорого!</t>
+          <t>Качество мебели очень порадовало. Каждый гость в нашем доме замечает, что гарнитур и шкафы сделаны добротно, стильно и удобно. Дизайнер учитывала все наши пожелания, на вопросы быстро отвечала. Сотрудники Авроры всегда на связи, держали в курсе статуса заказа. Сроки все были соблюдены. Мы безумно счастливы! Спасибо за уют в нашем доме!</t>
         </is>
       </c>
       <c r="E45" t="inlineStr">
@@ -3413,7 +3549,7 @@
       </c>
       <c r="L45" t="inlineStr">
         <is>
-          <t>Быстрая</t>
+          <t>Нет</t>
         </is>
       </c>
       <c r="M45" t="inlineStr">
@@ -3429,229 +3565,19 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>5415</v>
+        <v>1063</v>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t xml:space="preserve">Импровизация </t>
+          <t xml:space="preserve">Парус </t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>5.0</t>
+          <t>1.0</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
-        <is>
-          <t>Здравствуйте!Хотели бы сказать отдельное спасибо мастеру по установке кухонного гарнитура Александру Пискайкину. Такие ответственные мастера своего дела большая редкость, потому что он выполнил свою работу так, как для себя.Очень кропотливо и внимательно произвел всю установку гарнитура и решил вопросы, которые возникли в процессе монтажа (неровные полы, стены и т.д.)...мастер с большим опытом работы выполнил все в лучшем виде. Отдельное спасибо менеджеру Алене, которая также помогла в выборе и решила вопросы по доп. материалам. Работа сервиса данного мебельного салона на высоком уровне, сроки доставки ориентированы на клиента (за что отделье спасибо!!!!), все вопросы решаются мгновенно.Очень рады что остановились на Вашем салоне мебели!Радуемся новой кухне😊Александр, еще раз спасибо!!!Очень рекомендуем данного мастера!!!!!!</t>
-        </is>
-      </c>
-      <c r="E46" t="inlineStr">
-        <is>
-          <t>позитив</t>
-        </is>
-      </c>
-      <c r="F46" t="inlineStr">
-        <is>
-          <t>нет</t>
-        </is>
-      </c>
-      <c r="G46" t="inlineStr">
-        <is>
-          <t>нет</t>
-        </is>
-      </c>
-      <c r="H46" t="inlineStr">
-        <is>
-          <t>нет возврата</t>
-        </is>
-      </c>
-      <c r="I46" t="inlineStr">
-        <is>
-          <t>корпусная</t>
-        </is>
-      </c>
-      <c r="J46" t="inlineStr">
-        <is>
-          <t>Позитив</t>
-        </is>
-      </c>
-      <c r="K46" t="inlineStr">
-        <is>
-          <t>Нет</t>
-        </is>
-      </c>
-      <c r="L46" t="inlineStr">
-        <is>
-          <t>Быстрая</t>
-        </is>
-      </c>
-      <c r="M46" t="inlineStr">
-        <is>
-          <t>Нет возврата</t>
-        </is>
-      </c>
-      <c r="N46" t="inlineStr">
-        <is>
-          <t>Корпусная</t>
-        </is>
-      </c>
-    </row>
-    <row r="47">
-      <c r="A47" t="n">
-        <v>5481</v>
-      </c>
-      <c r="B47" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Divan Boss </t>
-        </is>
-      </c>
-      <c r="C47" t="inlineStr">
-        <is>
-          <t>1.0</t>
-        </is>
-      </c>
-      <c r="D47" t="inlineStr">
-        <is>
-          <t>Читайте отзывы, пожалуйста, прежде чем покупать в салонах и вообще читайте, штудируйте все и везде, прежде чем что-то где-то покупать.сейчас большинство фабрик работают, к сожалению, не на качество!!!Вот мы лоханулись😂….. но блииииин,у нас не возникло никаких сомнений, потому как пошли в салон по рекомендации людей, которые были в восторге от мебели, и мы даже не задумались, что может что-то пойти не так🤪 покупали диван 2 мая, доставка была 25.06, продавец заверяла, что доставка около 3-х недель, ну ладно ждем…. Периодически спрашиваем ,что там по доставке… ждите, диван уже на складе, скоро привезут, ну вот настало ЭТО СКОРО 18 июня🤣пришло сообщение от курьерской службы - диван доставим с такого то часа по такой-то… прошло 18 число, ничего не привезли… никто не предупредил даже что доставка задерживается, ничего не привезем и тд!!!!! Приходит сообщение -ждите доставку 25 июня, позвонили в магазин -точно ли доставка на 25 июня или опять нас так же опрокинут?!?! Столько букв в одно сообщение не вместится, надо выговорится и описать все в подробностях может руководство магазина обратит внимание?!?!?! Или все потеряно окончательно для этого магазина?!?!? ПРОДОЛЖЕНИИ ИСТОРИИ НИЖЕ В КОММЕНТАРИЯХ…⬇️</t>
-        </is>
-      </c>
-      <c r="E47" t="inlineStr">
-        <is>
-          <t>негатив</t>
-        </is>
-      </c>
-      <c r="F47" t="inlineStr">
-        <is>
-          <t>сервис</t>
-        </is>
-      </c>
-      <c r="G47" t="inlineStr">
-        <is>
-          <t>медленная</t>
-        </is>
-      </c>
-      <c r="H47" t="inlineStr">
-        <is>
-          <t>нет возврата</t>
-        </is>
-      </c>
-      <c r="I47" t="inlineStr">
-        <is>
-          <t>мягкая</t>
-        </is>
-      </c>
-      <c r="J47" t="inlineStr">
-        <is>
-          <t>Негатив</t>
-        </is>
-      </c>
-      <c r="K47" t="inlineStr">
-        <is>
-          <t>Сервис</t>
-        </is>
-      </c>
-      <c r="L47" t="inlineStr">
-        <is>
-          <t>Медленная</t>
-        </is>
-      </c>
-      <c r="M47" t="inlineStr">
-        <is>
-          <t>Нет возврата</t>
-        </is>
-      </c>
-      <c r="N47" t="inlineStr">
-        <is>
-          <t>Мягкая</t>
-        </is>
-      </c>
-    </row>
-    <row r="48">
-      <c r="A48" t="n">
-        <v>7260</v>
-      </c>
-      <c r="B48" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Аврора </t>
-        </is>
-      </c>
-      <c r="C48" t="inlineStr">
-        <is>
-          <t>5.0</t>
-        </is>
-      </c>
-      <c r="D48" t="inlineStr">
-        <is>
-          <t>Качество мебели очень порадовало. Каждый гость в нашем доме замечает, что гарнитур и шкафы сделаны добротно, стильно и удобно. Дизайнер учитывала все наши пожелания, на вопросы быстро отвечала. Сотрудники Авроры всегда на связи, держали в курсе статуса заказа. Сроки все были соблюдены. Мы безумно счастливы! Спасибо за уют в нашем доме!</t>
-        </is>
-      </c>
-      <c r="E48" t="inlineStr">
-        <is>
-          <t>позитив</t>
-        </is>
-      </c>
-      <c r="F48" t="inlineStr">
-        <is>
-          <t>нет</t>
-        </is>
-      </c>
-      <c r="G48" t="inlineStr">
-        <is>
-          <t>быстрая</t>
-        </is>
-      </c>
-      <c r="H48" t="inlineStr">
-        <is>
-          <t>нет возврата</t>
-        </is>
-      </c>
-      <c r="I48" t="inlineStr">
-        <is>
-          <t>нет</t>
-        </is>
-      </c>
-      <c r="J48" t="inlineStr">
-        <is>
-          <t>Позитив</t>
-        </is>
-      </c>
-      <c r="K48" t="inlineStr">
-        <is>
-          <t>Нет</t>
-        </is>
-      </c>
-      <c r="L48" t="inlineStr">
-        <is>
-          <t>Нет</t>
-        </is>
-      </c>
-      <c r="M48" t="inlineStr">
-        <is>
-          <t>Нет возврата</t>
-        </is>
-      </c>
-      <c r="N48" t="inlineStr">
-        <is>
-          <t>Корпусная</t>
-        </is>
-      </c>
-    </row>
-    <row r="49">
-      <c r="A49" t="n">
-        <v>1063</v>
-      </c>
-      <c r="B49" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Парус </t>
-        </is>
-      </c>
-      <c r="C49" t="inlineStr">
-        <is>
-          <t>1.0</t>
-        </is>
-      </c>
-      <c r="D49" t="inlineStr">
         <is>
           <t>Отвратительное качество 🤦🏽‍♀️
 Делали кровать на заказ! Сначала провалился матрас ,
@@ -3660,213 +3586,213 @@
 Кровати нет даже полу года !!!</t>
         </is>
       </c>
-      <c r="E49" t="inlineStr">
+      <c r="E46" t="inlineStr">
         <is>
           <t>негатив</t>
         </is>
       </c>
-      <c r="F49" t="inlineStr">
+      <c r="F46" t="inlineStr">
         <is>
           <t>качество</t>
         </is>
       </c>
-      <c r="G49" t="inlineStr">
-        <is>
-          <t>нет</t>
-        </is>
-      </c>
-      <c r="H49" t="inlineStr">
-        <is>
-          <t>нет возврата</t>
-        </is>
-      </c>
-      <c r="I49" t="inlineStr">
-        <is>
-          <t>нет</t>
-        </is>
-      </c>
-      <c r="J49" t="inlineStr">
+      <c r="G46" t="inlineStr">
+        <is>
+          <t>нет</t>
+        </is>
+      </c>
+      <c r="H46" t="inlineStr">
+        <is>
+          <t>нет возврата</t>
+        </is>
+      </c>
+      <c r="I46" t="inlineStr">
+        <is>
+          <t>нет</t>
+        </is>
+      </c>
+      <c r="J46" t="inlineStr">
         <is>
           <t>Негатив</t>
         </is>
       </c>
-      <c r="K49" t="inlineStr">
+      <c r="K46" t="inlineStr">
         <is>
           <t>Качество</t>
         </is>
       </c>
-      <c r="L49" t="inlineStr">
-        <is>
-          <t>Нет</t>
-        </is>
-      </c>
-      <c r="M49" t="inlineStr">
+      <c r="L46" t="inlineStr">
+        <is>
+          <t>Нет</t>
+        </is>
+      </c>
+      <c r="M46" t="inlineStr">
         <is>
           <t>Брак</t>
         </is>
       </c>
-      <c r="N49" t="inlineStr">
+      <c r="N46" t="inlineStr">
         <is>
           <t>Корпусная</t>
         </is>
       </c>
     </row>
-    <row r="50">
-      <c r="A50" t="n">
+    <row r="47">
+      <c r="A47" t="n">
         <v>7845</v>
       </c>
-      <c r="B50" t="inlineStr">
+      <c r="B47" t="inlineStr">
         <is>
           <t xml:space="preserve">Dizara </t>
         </is>
       </c>
-      <c r="C50" t="inlineStr">
+      <c r="C47" t="inlineStr">
         <is>
           <t>1.0</t>
         </is>
       </c>
-      <c r="D50" t="inlineStr">
+      <c r="D47" t="inlineStr">
         <is>
           <t>Для желающих приобрести мебель на заказ, диваны и т.п, готовьтесь к тому, что ожидание будет не менее 3-х месяцев, все убеждения консультантов про один месяц и диван будет у вас, просто трёп, главное принять заказ, а потом в течении долгого времени одна и та же речь, сперва что диван готов, на неделе должны привести, потом через неделю проблемы с логистикой, ещё через неделю оказывается на фабрике нужная ткань закончилась (как то странно что это обнаружилось спустя уже 2 месяца), потом снова машина с Красноярска месяц не могла выехать, и так постоянно. В общем, решились на покупку в этом месте из за быстрого срока изготовления, но по факту это просто замануха. Если готовы ждать, то мебель впринципе неплохая, проблем в качестве не выявили.
 Мы не были готовы к такому сроку ожидания доставки, поэтому если бы изначально нам сообщили как это будет по факту, то даже не обратились бы сюда</t>
         </is>
       </c>
-      <c r="E50" t="inlineStr">
+      <c r="E47" t="inlineStr">
         <is>
           <t>негатив</t>
         </is>
       </c>
-      <c r="F50" t="inlineStr">
+      <c r="F47" t="inlineStr">
         <is>
           <t>сервис</t>
         </is>
       </c>
-      <c r="G50" t="inlineStr">
+      <c r="G47" t="inlineStr">
         <is>
           <t>медленная</t>
         </is>
       </c>
-      <c r="H50" t="inlineStr">
-        <is>
-          <t>нет возврата</t>
-        </is>
-      </c>
-      <c r="I50" t="inlineStr">
+      <c r="H47" t="inlineStr">
+        <is>
+          <t>нет возврата</t>
+        </is>
+      </c>
+      <c r="I47" t="inlineStr">
         <is>
           <t>мягкая</t>
         </is>
       </c>
-      <c r="J50" t="inlineStr">
+      <c r="J47" t="inlineStr">
         <is>
           <t>Негатив</t>
         </is>
       </c>
-      <c r="K50" t="inlineStr">
+      <c r="K47" t="inlineStr">
         <is>
           <t>Сервис</t>
         </is>
       </c>
-      <c r="L50" t="inlineStr">
+      <c r="L47" t="inlineStr">
         <is>
           <t>Медленная</t>
         </is>
       </c>
-      <c r="M50" t="inlineStr">
-        <is>
-          <t>Нет возврата</t>
-        </is>
-      </c>
-      <c r="N50" t="inlineStr">
+      <c r="M47" t="inlineStr">
+        <is>
+          <t>Нет возврата</t>
+        </is>
+      </c>
+      <c r="N47" t="inlineStr">
         <is>
           <t>Мягкая</t>
         </is>
       </c>
     </row>
-    <row r="51">
-      <c r="A51" t="n">
+    <row r="48">
+      <c r="A48" t="n">
         <v>8507</v>
       </c>
-      <c r="B51" t="inlineStr">
+      <c r="B48" t="inlineStr">
         <is>
           <t>Галерея плюс</t>
         </is>
       </c>
-      <c r="C51" t="inlineStr">
+      <c r="C48" t="inlineStr">
         <is>
           <t>5.0</t>
         </is>
       </c>
-      <c r="D51" t="inlineStr">
+      <c r="D48" t="inlineStr">
         <is>
           <t>Хорошая бюджетная мебель. Цена ниже, чем в других магазинах.</t>
         </is>
       </c>
-      <c r="E51" t="inlineStr">
+      <c r="E48" t="inlineStr">
         <is>
           <t>позитив</t>
         </is>
       </c>
-      <c r="F51" t="inlineStr">
-        <is>
-          <t>нет</t>
-        </is>
-      </c>
-      <c r="G51" t="inlineStr">
-        <is>
-          <t>нет</t>
-        </is>
-      </c>
-      <c r="H51" t="inlineStr">
-        <is>
-          <t>нет возврата</t>
-        </is>
-      </c>
-      <c r="I51" t="inlineStr">
-        <is>
-          <t>нет</t>
-        </is>
-      </c>
-      <c r="J51" t="inlineStr">
+      <c r="F48" t="inlineStr">
+        <is>
+          <t>нет</t>
+        </is>
+      </c>
+      <c r="G48" t="inlineStr">
+        <is>
+          <t>нет</t>
+        </is>
+      </c>
+      <c r="H48" t="inlineStr">
+        <is>
+          <t>нет возврата</t>
+        </is>
+      </c>
+      <c r="I48" t="inlineStr">
+        <is>
+          <t>нет</t>
+        </is>
+      </c>
+      <c r="J48" t="inlineStr">
         <is>
           <t>Позитив</t>
         </is>
       </c>
-      <c r="K51" t="inlineStr">
-        <is>
-          <t>Нет</t>
-        </is>
-      </c>
-      <c r="L51" t="inlineStr">
-        <is>
-          <t>Нет</t>
-        </is>
-      </c>
-      <c r="M51" t="inlineStr">
-        <is>
-          <t>Нет возврата</t>
-        </is>
-      </c>
-      <c r="N51" t="inlineStr">
-        <is>
-          <t>Нет</t>
-        </is>
-      </c>
-    </row>
-    <row r="52">
-      <c r="A52" t="n">
+      <c r="K48" t="inlineStr">
+        <is>
+          <t>Нет</t>
+        </is>
+      </c>
+      <c r="L48" t="inlineStr">
+        <is>
+          <t>Нет</t>
+        </is>
+      </c>
+      <c r="M48" t="inlineStr">
+        <is>
+          <t>Нет возврата</t>
+        </is>
+      </c>
+      <c r="N48" t="inlineStr">
+        <is>
+          <t>Нет</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="n">
         <v>2656</v>
       </c>
-      <c r="B52" t="inlineStr">
+      <c r="B49" t="inlineStr">
         <is>
           <t xml:space="preserve">Ваш уют </t>
         </is>
       </c>
-      <c r="C52" t="inlineStr">
+      <c r="C49" t="inlineStr">
         <is>
           <t>1.0</t>
         </is>
       </c>
-      <c r="D52" t="inlineStr">
+      <c r="D49" t="inlineStr">
         <is>
           <t>Заказал тумбу в ванную в конце июля. Монтажа пришлось ждать почти месяц. Но и смонтировав, мастер не отрегулировал дверцы и обозначил дефектный толкатель. Сказал, что передаст по смене и послезавтра край, приедет мастер и все доделает.
 Итог.
@@ -3876,14 +3802,225 @@
 Заказывал в этой фирме несколько шкафов и кухню ранее - прекрасно все было. Видимо пришло время испортиться.</t>
         </is>
       </c>
+      <c r="E49" t="inlineStr">
+        <is>
+          <t>негатив</t>
+        </is>
+      </c>
+      <c r="F49" t="inlineStr">
+        <is>
+          <t>сервис</t>
+        </is>
+      </c>
+      <c r="G49" t="inlineStr">
+        <is>
+          <t>нет</t>
+        </is>
+      </c>
+      <c r="H49" t="inlineStr">
+        <is>
+          <t>нет возврата</t>
+        </is>
+      </c>
+      <c r="I49" t="inlineStr">
+        <is>
+          <t>нет</t>
+        </is>
+      </c>
+      <c r="J49" t="inlineStr">
+        <is>
+          <t>Негатив</t>
+        </is>
+      </c>
+      <c r="K49" t="inlineStr">
+        <is>
+          <t>Сервис</t>
+        </is>
+      </c>
+      <c r="L49" t="inlineStr">
+        <is>
+          <t>Медленная</t>
+        </is>
+      </c>
+      <c r="M49" t="inlineStr">
+        <is>
+          <t>Нет возврата</t>
+        </is>
+      </c>
+      <c r="N49" t="inlineStr">
+        <is>
+          <t>Корпусная</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="n">
+        <v>7288</v>
+      </c>
+      <c r="B50" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Аврора </t>
+        </is>
+      </c>
+      <c r="C50" t="inlineStr">
+        <is>
+          <t>5.0</t>
+        </is>
+      </c>
+      <c r="D50" t="inlineStr">
+        <is>
+          <t>Отличная фабрика. Уже не первый раз там заказываем. То себе , то маме, сейчас вот решили сделать гардеробную. В целом вышло достаточно гармонично. Спасибо ещё раз, Вы супер.</t>
+        </is>
+      </c>
+      <c r="E50" t="inlineStr">
+        <is>
+          <t>позитив</t>
+        </is>
+      </c>
+      <c r="F50" t="inlineStr">
+        <is>
+          <t>нет</t>
+        </is>
+      </c>
+      <c r="G50" t="inlineStr">
+        <is>
+          <t>нет</t>
+        </is>
+      </c>
+      <c r="H50" t="inlineStr">
+        <is>
+          <t>нет возврата</t>
+        </is>
+      </c>
+      <c r="I50" t="inlineStr">
+        <is>
+          <t>корпусная</t>
+        </is>
+      </c>
+      <c r="J50" t="inlineStr">
+        <is>
+          <t>Позитив</t>
+        </is>
+      </c>
+      <c r="K50" t="inlineStr">
+        <is>
+          <t>Нет</t>
+        </is>
+      </c>
+      <c r="L50" t="inlineStr">
+        <is>
+          <t>Нет</t>
+        </is>
+      </c>
+      <c r="M50" t="inlineStr">
+        <is>
+          <t>Нет возврата</t>
+        </is>
+      </c>
+      <c r="N50" t="inlineStr">
+        <is>
+          <t>Корпусная</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" t="n">
+        <v>8631</v>
+      </c>
+      <c r="B51" t="inlineStr">
+        <is>
+          <t>Эталон</t>
+        </is>
+      </c>
+      <c r="C51" t="inlineStr">
+        <is>
+          <t>5.0</t>
+        </is>
+      </c>
+      <c r="D51" t="inlineStr">
+        <is>
+          <t>Заказывала кухню, можно приобрести качественную мебель, но дорого.</t>
+        </is>
+      </c>
+      <c r="E51" t="inlineStr">
+        <is>
+          <t>позитив</t>
+        </is>
+      </c>
+      <c r="F51" t="inlineStr">
+        <is>
+          <t>нет</t>
+        </is>
+      </c>
+      <c r="G51" t="inlineStr">
+        <is>
+          <t>нет</t>
+        </is>
+      </c>
+      <c r="H51" t="inlineStr">
+        <is>
+          <t>нет возврата</t>
+        </is>
+      </c>
+      <c r="I51" t="inlineStr">
+        <is>
+          <t>корпусная</t>
+        </is>
+      </c>
+      <c r="J51" t="inlineStr">
+        <is>
+          <t>Нейтрально</t>
+        </is>
+      </c>
+      <c r="K51" t="inlineStr">
+        <is>
+          <t>Иное</t>
+        </is>
+      </c>
+      <c r="L51" t="inlineStr">
+        <is>
+          <t>Нет</t>
+        </is>
+      </c>
+      <c r="M51" t="inlineStr">
+        <is>
+          <t>Нет возврата</t>
+        </is>
+      </c>
+      <c r="N51" t="inlineStr">
+        <is>
+          <t>Корпусная</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" t="n">
+        <v>5936</v>
+      </c>
+      <c r="B52" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Мир мебели </t>
+        </is>
+      </c>
+      <c r="C52" t="inlineStr">
+        <is>
+          <t>4.0</t>
+        </is>
+      </c>
+      <c r="D52" t="inlineStr">
+        <is>
+          <t>Осталась довольна кухней которую приобрела в Мир мебели (Версаль)у дизайнера продавца Сергея , умеет воплотить мечты в проект а потом и в реальную кухню) и самое главное понять что от него хочет покупатель!
+Очень довольна, буду рекомендовать своим знакомым такого дизайнера как Сергей)</t>
+        </is>
+      </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>негатив</t>
+          <t>позитив</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>сервис</t>
+          <t>нет</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
@@ -3898,22 +4035,22 @@
       </c>
       <c r="I52" t="inlineStr">
         <is>
-          <t>нет</t>
+          <t>корпусная</t>
         </is>
       </c>
       <c r="J52" t="inlineStr">
         <is>
-          <t>Негатив</t>
+          <t>Позитив</t>
         </is>
       </c>
       <c r="K52" t="inlineStr">
         <is>
-          <t>Сервис</t>
+          <t>Нет</t>
         </is>
       </c>
       <c r="L52" t="inlineStr">
         <is>
-          <t>Медленная</t>
+          <t>Нет</t>
         </is>
       </c>
       <c r="M52" t="inlineStr">
@@ -3929,31 +4066,31 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>7288</v>
+        <v>2029</v>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t xml:space="preserve">Аврора </t>
+          <t xml:space="preserve">Сарма </t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>5.0</t>
+          <t>1.0</t>
         </is>
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>Отличная фабрика. Уже не первый раз там заказываем. То себе , то маме, сейчас вот решили сделать гардеробную. В целом вышло достаточно гармонично. Спасибо ещё раз, Вы супер.</t>
+          <t>Мы разочарованы работой компании, покупали шкаф, нам не доложили фурнитуру, теперь дверь крепить не на что. Не смотря на то, что обратились в тот же день, когда и собирали шкаф, наше обращение рассматривали месяц, в итоге спустя МЕСЯЦ с нас потребовали бирки от коробок, которых конечно же уже не было. Не понятно, почему нам не могли сказать про бирки при первом же обращении,когда коробки ещё лежали дома. В итоге комплектовщики свою работу выполнили плохо, а разбираться с последствиями их работы приходится нам. Придётся покупать самостоятельно эту фурнитуру, хотя за неё уже было заплачено.</t>
         </is>
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>позитив</t>
+          <t>негатив</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>нет</t>
+          <t>сервис</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
@@ -3973,12 +4110,12 @@
       </c>
       <c r="J53" t="inlineStr">
         <is>
-          <t>Позитив</t>
+          <t>Негатив</t>
         </is>
       </c>
       <c r="K53" t="inlineStr">
         <is>
-          <t>Нет</t>
+          <t>Сервис</t>
         </is>
       </c>
       <c r="L53" t="inlineStr">
@@ -3988,7 +4125,7 @@
       </c>
       <c r="M53" t="inlineStr">
         <is>
-          <t>Нет возврата</t>
+          <t>Другое</t>
         </is>
       </c>
       <c r="N53" t="inlineStr">
@@ -3999,11 +4136,11 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>8631</v>
+        <v>7699</v>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>Эталон</t>
+          <t xml:space="preserve">Пинскдрев </t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
@@ -4012,269 +4149,6 @@
         </is>
       </c>
       <c r="D54" t="inlineStr">
-        <is>
-          <t>Заказывала кухню, можно приобрести качественную мебель, но дорого.</t>
-        </is>
-      </c>
-      <c r="E54" t="inlineStr">
-        <is>
-          <t>позитив</t>
-        </is>
-      </c>
-      <c r="F54" t="inlineStr">
-        <is>
-          <t>нет</t>
-        </is>
-      </c>
-      <c r="G54" t="inlineStr">
-        <is>
-          <t>нет</t>
-        </is>
-      </c>
-      <c r="H54" t="inlineStr">
-        <is>
-          <t>нет возврата</t>
-        </is>
-      </c>
-      <c r="I54" t="inlineStr">
-        <is>
-          <t>корпусная</t>
-        </is>
-      </c>
-      <c r="J54" t="inlineStr">
-        <is>
-          <t>Нейтрально</t>
-        </is>
-      </c>
-      <c r="K54" t="inlineStr">
-        <is>
-          <t>Иное</t>
-        </is>
-      </c>
-      <c r="L54" t="inlineStr">
-        <is>
-          <t>Нет</t>
-        </is>
-      </c>
-      <c r="M54" t="inlineStr">
-        <is>
-          <t>Нет возврата</t>
-        </is>
-      </c>
-      <c r="N54" t="inlineStr">
-        <is>
-          <t>Корпусная</t>
-        </is>
-      </c>
-    </row>
-    <row r="55">
-      <c r="A55" t="n">
-        <v>5936</v>
-      </c>
-      <c r="B55" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Мир мебели </t>
-        </is>
-      </c>
-      <c r="C55" t="inlineStr">
-        <is>
-          <t>4.0</t>
-        </is>
-      </c>
-      <c r="D55" t="inlineStr">
-        <is>
-          <t>Осталась довольна кухней которую приобрела в Мир мебели (Версаль)у дизайнера продавца Сергея , умеет воплотить мечты в проект а потом и в реальную кухню) и самое главное понять что от него хочет покупатель!
-Очень довольна, буду рекомендовать своим знакомым такого дизайнера как Сергей)</t>
-        </is>
-      </c>
-      <c r="E55" t="inlineStr">
-        <is>
-          <t>позитив</t>
-        </is>
-      </c>
-      <c r="F55" t="inlineStr">
-        <is>
-          <t>нет</t>
-        </is>
-      </c>
-      <c r="G55" t="inlineStr">
-        <is>
-          <t>нет</t>
-        </is>
-      </c>
-      <c r="H55" t="inlineStr">
-        <is>
-          <t>нет возврата</t>
-        </is>
-      </c>
-      <c r="I55" t="inlineStr">
-        <is>
-          <t>корпусная</t>
-        </is>
-      </c>
-      <c r="J55" t="inlineStr">
-        <is>
-          <t>Позитив</t>
-        </is>
-      </c>
-      <c r="K55" t="inlineStr">
-        <is>
-          <t>Нет</t>
-        </is>
-      </c>
-      <c r="L55" t="inlineStr">
-        <is>
-          <t>Нет</t>
-        </is>
-      </c>
-      <c r="M55" t="inlineStr">
-        <is>
-          <t>Нет возврата</t>
-        </is>
-      </c>
-      <c r="N55" t="inlineStr">
-        <is>
-          <t>Корпусная</t>
-        </is>
-      </c>
-    </row>
-    <row r="56">
-      <c r="A56" t="n">
-        <v>12147</v>
-      </c>
-      <c r="B56" t="inlineStr">
-        <is>
-          <t>Мебель Холл</t>
-        </is>
-      </c>
-      <c r="C56" t="inlineStr">
-        <is>
-          <t>5 звезд</t>
-        </is>
-      </c>
-      <c r="D56" t="inlineStr"/>
-      <c r="E56" t="inlineStr"/>
-      <c r="F56" t="inlineStr"/>
-      <c r="G56" t="inlineStr"/>
-      <c r="H56" t="inlineStr"/>
-      <c r="I56" t="inlineStr"/>
-      <c r="J56" t="inlineStr"/>
-      <c r="K56" t="inlineStr"/>
-      <c r="L56" t="inlineStr"/>
-      <c r="M56" t="inlineStr"/>
-      <c r="N56" t="inlineStr"/>
-    </row>
-    <row r="57">
-      <c r="A57" t="n">
-        <v>2029</v>
-      </c>
-      <c r="B57" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Сарма </t>
-        </is>
-      </c>
-      <c r="C57" t="inlineStr">
-        <is>
-          <t>1.0</t>
-        </is>
-      </c>
-      <c r="D57" t="inlineStr">
-        <is>
-          <t>Мы разочарованы работой компании, покупали шкаф, нам не доложили фурнитуру, теперь дверь крепить не на что. Не смотря на то, что обратились в тот же день, когда и собирали шкаф, наше обращение рассматривали месяц, в итоге спустя МЕСЯЦ с нас потребовали бирки от коробок, которых конечно же уже не было. Не понятно, почему нам не могли сказать про бирки при первом же обращении,когда коробки ещё лежали дома. В итоге комплектовщики свою работу выполнили плохо, а разбираться с последствиями их работы приходится нам. Придётся покупать самостоятельно эту фурнитуру, хотя за неё уже было заплачено.</t>
-        </is>
-      </c>
-      <c r="E57" t="inlineStr">
-        <is>
-          <t>негатив</t>
-        </is>
-      </c>
-      <c r="F57" t="inlineStr">
-        <is>
-          <t>сервис</t>
-        </is>
-      </c>
-      <c r="G57" t="inlineStr">
-        <is>
-          <t>нет</t>
-        </is>
-      </c>
-      <c r="H57" t="inlineStr">
-        <is>
-          <t>нет возврата</t>
-        </is>
-      </c>
-      <c r="I57" t="inlineStr">
-        <is>
-          <t>корпусная</t>
-        </is>
-      </c>
-      <c r="J57" t="inlineStr">
-        <is>
-          <t>Негатив</t>
-        </is>
-      </c>
-      <c r="K57" t="inlineStr">
-        <is>
-          <t>Сервис</t>
-        </is>
-      </c>
-      <c r="L57" t="inlineStr">
-        <is>
-          <t>Нет</t>
-        </is>
-      </c>
-      <c r="M57" t="inlineStr">
-        <is>
-          <t>Другое</t>
-        </is>
-      </c>
-      <c r="N57" t="inlineStr">
-        <is>
-          <t>Корпусная</t>
-        </is>
-      </c>
-    </row>
-    <row r="58">
-      <c r="A58" t="n">
-        <v>12044</v>
-      </c>
-      <c r="B58" t="inlineStr">
-        <is>
-          <t>Магазин Мебели "Москва".</t>
-        </is>
-      </c>
-      <c r="C58" t="inlineStr">
-        <is>
-          <t>5 звезд</t>
-        </is>
-      </c>
-      <c r="D58" t="inlineStr"/>
-      <c r="E58" t="inlineStr"/>
-      <c r="F58" t="inlineStr"/>
-      <c r="G58" t="inlineStr"/>
-      <c r="H58" t="inlineStr"/>
-      <c r="I58" t="inlineStr"/>
-      <c r="J58" t="inlineStr"/>
-      <c r="K58" t="inlineStr"/>
-      <c r="L58" t="inlineStr"/>
-      <c r="M58" t="inlineStr"/>
-      <c r="N58" t="inlineStr"/>
-    </row>
-    <row r="59">
-      <c r="A59" t="n">
-        <v>7699</v>
-      </c>
-      <c r="B59" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Пинскдрев </t>
-        </is>
-      </c>
-      <c r="C59" t="inlineStr">
-        <is>
-          <t>5.0</t>
-        </is>
-      </c>
-      <c r="D59" t="inlineStr">
         <is>
           <t>Приобрели кровать в данном магазине
 Шикарная,отличное качество,очень удобная 👍
@@ -4282,226 +4156,576 @@
 Ставлю высшую оценку магазину</t>
         </is>
       </c>
-      <c r="E59" t="inlineStr">
+      <c r="E54" t="inlineStr">
         <is>
           <t>позитив</t>
         </is>
       </c>
-      <c r="F59" t="inlineStr">
-        <is>
-          <t>нет</t>
-        </is>
-      </c>
-      <c r="G59" t="inlineStr">
-        <is>
-          <t>нет</t>
-        </is>
-      </c>
-      <c r="H59" t="inlineStr">
-        <is>
-          <t>нет возврата</t>
-        </is>
-      </c>
-      <c r="I59" t="inlineStr">
-        <is>
-          <t>нет</t>
-        </is>
-      </c>
-      <c r="J59" t="inlineStr">
+      <c r="F54" t="inlineStr">
+        <is>
+          <t>нет</t>
+        </is>
+      </c>
+      <c r="G54" t="inlineStr">
+        <is>
+          <t>нет</t>
+        </is>
+      </c>
+      <c r="H54" t="inlineStr">
+        <is>
+          <t>нет возврата</t>
+        </is>
+      </c>
+      <c r="I54" t="inlineStr">
+        <is>
+          <t>нет</t>
+        </is>
+      </c>
+      <c r="J54" t="inlineStr">
         <is>
           <t>Позитив</t>
         </is>
       </c>
-      <c r="K59" t="inlineStr">
-        <is>
-          <t>Нет</t>
-        </is>
-      </c>
-      <c r="L59" t="inlineStr">
-        <is>
-          <t>Нет</t>
-        </is>
-      </c>
-      <c r="M59" t="inlineStr">
-        <is>
-          <t>Нет возврата</t>
-        </is>
-      </c>
-      <c r="N59" t="inlineStr">
+      <c r="K54" t="inlineStr">
+        <is>
+          <t>Нет</t>
+        </is>
+      </c>
+      <c r="L54" t="inlineStr">
+        <is>
+          <t>Нет</t>
+        </is>
+      </c>
+      <c r="M54" t="inlineStr">
+        <is>
+          <t>Нет возврата</t>
+        </is>
+      </c>
+      <c r="N54" t="inlineStr">
         <is>
           <t>Корпусная</t>
         </is>
       </c>
     </row>
-    <row r="60">
-      <c r="A60" t="n">
+    <row r="55">
+      <c r="A55" t="n">
         <v>7140</v>
       </c>
-      <c r="B60" t="inlineStr">
+      <c r="B55" t="inlineStr">
         <is>
           <t xml:space="preserve">Аврора </t>
         </is>
       </c>
-      <c r="C60" t="inlineStr">
+      <c r="C55" t="inlineStr">
         <is>
           <t>5.0</t>
         </is>
       </c>
-      <c r="D60" t="inlineStr">
+      <c r="D55" t="inlineStr">
         <is>
           <t>Заказали гардероб, в восторге от цены и качества! Стоит отметить, что сотрудники компании вошли в положение и выполнили заказ в максимально короткие сроки, большое спасибо за отзывчивость!</t>
         </is>
       </c>
-      <c r="E60" t="inlineStr">
+      <c r="E55" t="inlineStr">
         <is>
           <t>позитив</t>
         </is>
       </c>
-      <c r="F60" t="inlineStr">
-        <is>
-          <t>нет</t>
-        </is>
-      </c>
-      <c r="G60" t="inlineStr">
+      <c r="F55" t="inlineStr">
+        <is>
+          <t>нет</t>
+        </is>
+      </c>
+      <c r="G55" t="inlineStr">
         <is>
           <t>быстрая</t>
         </is>
       </c>
-      <c r="H60" t="inlineStr">
-        <is>
-          <t>нет возврата</t>
-        </is>
-      </c>
-      <c r="I60" t="inlineStr">
+      <c r="H55" t="inlineStr">
+        <is>
+          <t>нет возврата</t>
+        </is>
+      </c>
+      <c r="I55" t="inlineStr">
         <is>
           <t>корпусная</t>
         </is>
       </c>
-      <c r="J60" t="inlineStr">
+      <c r="J55" t="inlineStr">
         <is>
           <t>Позитив</t>
         </is>
       </c>
-      <c r="K60" t="inlineStr">
-        <is>
-          <t>Нет</t>
-        </is>
-      </c>
-      <c r="L60" t="inlineStr">
+      <c r="K55" t="inlineStr">
+        <is>
+          <t>Нет</t>
+        </is>
+      </c>
+      <c r="L55" t="inlineStr">
         <is>
           <t>Быстрая</t>
         </is>
       </c>
-      <c r="M60" t="inlineStr">
-        <is>
-          <t>Нет возврата</t>
-        </is>
-      </c>
-      <c r="N60" t="inlineStr">
+      <c r="M55" t="inlineStr">
+        <is>
+          <t>Нет возврата</t>
+        </is>
+      </c>
+      <c r="N55" t="inlineStr">
         <is>
           <t>Корпусная</t>
         </is>
       </c>
     </row>
-    <row r="61">
-      <c r="A61" t="n">
+    <row r="56">
+      <c r="A56" t="n">
         <v>2867</v>
       </c>
-      <c r="B61" t="inlineStr">
+      <c r="B56" t="inlineStr">
         <is>
           <t xml:space="preserve">Viko </t>
         </is>
       </c>
-      <c r="C61" t="inlineStr">
+      <c r="C56" t="inlineStr">
         <is>
           <t>5.0</t>
         </is>
       </c>
-      <c r="D61" t="inlineStr">
+      <c r="D56" t="inlineStr">
         <is>
           <t>Купили диван "Гамлет 2" под заказ.Консультант помогла выбрать модель и ткань,сориентировала по срокам доставки.Порадовала предоплата в 1000р и шоколадка )).Диван пришел в срок и в выбранной ткани.Доставка без нареканий.Всем довольны.Заказали еще и реставрацию.Рекомендую.</t>
         </is>
       </c>
-      <c r="E61" t="inlineStr">
+      <c r="E56" t="inlineStr">
         <is>
           <t>позитив</t>
         </is>
       </c>
-      <c r="F61" t="inlineStr">
-        <is>
-          <t>нет</t>
-        </is>
-      </c>
-      <c r="G61" t="inlineStr">
+      <c r="F56" t="inlineStr">
+        <is>
+          <t>нет</t>
+        </is>
+      </c>
+      <c r="G56" t="inlineStr">
         <is>
           <t>быстрая</t>
         </is>
       </c>
-      <c r="H61" t="inlineStr">
-        <is>
-          <t>нет возврата</t>
-        </is>
-      </c>
-      <c r="I61" t="inlineStr">
+      <c r="H56" t="inlineStr">
+        <is>
+          <t>нет возврата</t>
+        </is>
+      </c>
+      <c r="I56" t="inlineStr">
         <is>
           <t>мягкая</t>
         </is>
       </c>
-      <c r="J61" t="inlineStr">
+      <c r="J56" t="inlineStr">
         <is>
           <t>Позитив</t>
         </is>
       </c>
-      <c r="K61" t="inlineStr">
-        <is>
-          <t>Нет</t>
-        </is>
-      </c>
-      <c r="L61" t="inlineStr">
+      <c r="K56" t="inlineStr">
+        <is>
+          <t>Нет</t>
+        </is>
+      </c>
+      <c r="L56" t="inlineStr">
         <is>
           <t>Быстрая</t>
         </is>
       </c>
-      <c r="M61" t="inlineStr">
-        <is>
-          <t>Нет возврата</t>
-        </is>
-      </c>
-      <c r="N61" t="inlineStr">
+      <c r="M56" t="inlineStr">
+        <is>
+          <t>Нет возврата</t>
+        </is>
+      </c>
+      <c r="N56" t="inlineStr">
         <is>
           <t>Мягкая</t>
         </is>
       </c>
     </row>
-    <row r="62">
-      <c r="A62" t="n">
+    <row r="57">
+      <c r="A57" t="n">
         <v>3439</v>
       </c>
-      <c r="B62" t="inlineStr">
+      <c r="B57" t="inlineStr">
         <is>
           <t xml:space="preserve">Магазин мебели </t>
         </is>
       </c>
-      <c r="C62" t="inlineStr">
+      <c r="C57" t="inlineStr">
         <is>
           <t>1.0</t>
         </is>
       </c>
-      <c r="D62" t="inlineStr">
+      <c r="D57" t="inlineStr">
         <is>
           <t>Работаю с сайтами и часто оцениваю их функциональность. За качество товара сказать не могу потому что ничего выбрать не смогла. Зашла на сайт, нет цены ни на один товар, мне уже неинтересно даже было рассматривать кровать сколько найти уже, куда спрятали цену, может есть «рассчитать по индивидуальным меркам» или «оставить заявку».
 Есть только позвонить напрямую и посмотреть пример мебели, а где цены искать, так и не нашла. Секретность, наверное, какая-то 😅 Потенциальному покупателю хочется прицениться, понять, хочет и может ли он у вас заказать.
 Затем прочла первый попавшийся негативный отзыв, на которые вы даже не дали клиенту ответ. Совет, работайте над имиджем и клиентоориентированностью!</t>
         </is>
       </c>
+      <c r="E57" t="inlineStr">
+        <is>
+          <t>негатив</t>
+        </is>
+      </c>
+      <c r="F57" t="inlineStr">
+        <is>
+          <t>сервис</t>
+        </is>
+      </c>
+      <c r="G57" t="inlineStr">
+        <is>
+          <t>нет</t>
+        </is>
+      </c>
+      <c r="H57" t="inlineStr">
+        <is>
+          <t>нет возврата</t>
+        </is>
+      </c>
+      <c r="I57" t="inlineStr">
+        <is>
+          <t>нет</t>
+        </is>
+      </c>
+      <c r="J57" t="inlineStr">
+        <is>
+          <t>Негатив</t>
+        </is>
+      </c>
+      <c r="K57" t="inlineStr">
+        <is>
+          <t>Сервис</t>
+        </is>
+      </c>
+      <c r="L57" t="inlineStr">
+        <is>
+          <t>Нет</t>
+        </is>
+      </c>
+      <c r="M57" t="inlineStr">
+        <is>
+          <t>Нет возврата</t>
+        </is>
+      </c>
+      <c r="N57" t="inlineStr">
+        <is>
+          <t>Корпусная</t>
+        </is>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" t="n">
+        <v>10274</v>
+      </c>
+      <c r="B58" t="inlineStr">
+        <is>
+          <t>Добрыня</t>
+        </is>
+      </c>
+      <c r="C58" t="inlineStr">
+        <is>
+          <t>5.0</t>
+        </is>
+      </c>
+      <c r="D58" t="inlineStr">
+        <is>
+          <t>Мне очень понравился этот магазин, доставили диван через час, консультант была очень доброй и отзывчивой девушкой. К сожалению, не помню, как её зовут</t>
+        </is>
+      </c>
+      <c r="E58" t="inlineStr">
+        <is>
+          <t>позитив</t>
+        </is>
+      </c>
+      <c r="F58" t="inlineStr">
+        <is>
+          <t>нет</t>
+        </is>
+      </c>
+      <c r="G58" t="inlineStr">
+        <is>
+          <t>быстрая</t>
+        </is>
+      </c>
+      <c r="H58" t="inlineStr">
+        <is>
+          <t>нет возврата</t>
+        </is>
+      </c>
+      <c r="I58" t="inlineStr">
+        <is>
+          <t>мягкая</t>
+        </is>
+      </c>
+      <c r="J58" t="inlineStr">
+        <is>
+          <t>Позитив</t>
+        </is>
+      </c>
+      <c r="K58" t="inlineStr">
+        <is>
+          <t>Нет</t>
+        </is>
+      </c>
+      <c r="L58" t="inlineStr">
+        <is>
+          <t>Быстрая</t>
+        </is>
+      </c>
+      <c r="M58" t="inlineStr">
+        <is>
+          <t>Нет возврата</t>
+        </is>
+      </c>
+      <c r="N58" t="inlineStr">
+        <is>
+          <t>Мягкая</t>
+        </is>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" t="n">
+        <v>6155</v>
+      </c>
+      <c r="B59" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Эргомаркет </t>
+        </is>
+      </c>
+      <c r="C59" t="inlineStr">
+        <is>
+          <t>5.0</t>
+        </is>
+      </c>
+      <c r="D59" t="inlineStr">
+        <is>
+          <t>Прекрасный магазин с огромным выбором ортопедической обуви для детей. Купили правильную обувь, цена вполне устроила</t>
+        </is>
+      </c>
+      <c r="E59" t="inlineStr">
+        <is>
+          <t>позитив</t>
+        </is>
+      </c>
+      <c r="F59" t="inlineStr">
+        <is>
+          <t>нет</t>
+        </is>
+      </c>
+      <c r="G59" t="inlineStr">
+        <is>
+          <t>нет</t>
+        </is>
+      </c>
+      <c r="H59" t="inlineStr">
+        <is>
+          <t>нет возврата</t>
+        </is>
+      </c>
+      <c r="I59" t="inlineStr">
+        <is>
+          <t>нет</t>
+        </is>
+      </c>
+      <c r="J59" t="inlineStr">
+        <is>
+          <t>Позитив</t>
+        </is>
+      </c>
+      <c r="K59" t="inlineStr">
+        <is>
+          <t>Нет</t>
+        </is>
+      </c>
+      <c r="L59" t="inlineStr">
+        <is>
+          <t>Нет</t>
+        </is>
+      </c>
+      <c r="M59" t="inlineStr">
+        <is>
+          <t>Нет возврата</t>
+        </is>
+      </c>
+      <c r="N59" t="inlineStr">
+        <is>
+          <t>Нет</t>
+        </is>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" t="n">
+        <v>7503</v>
+      </c>
+      <c r="B60" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Dizara </t>
+        </is>
+      </c>
+      <c r="C60" t="inlineStr">
+        <is>
+          <t>4.0</t>
+        </is>
+      </c>
+      <c r="D60" t="inlineStr">
+        <is>
+          <t>В целом все хорошо, немного затянули по срокам, но главное что мебель без дефектов и по размерам все как надо. Саму установку произвели быстро</t>
+        </is>
+      </c>
+      <c r="E60" t="inlineStr">
+        <is>
+          <t>позитив</t>
+        </is>
+      </c>
+      <c r="F60" t="inlineStr">
+        <is>
+          <t>нет</t>
+        </is>
+      </c>
+      <c r="G60" t="inlineStr">
+        <is>
+          <t>быстрая</t>
+        </is>
+      </c>
+      <c r="H60" t="inlineStr">
+        <is>
+          <t>нет возврата</t>
+        </is>
+      </c>
+      <c r="I60" t="inlineStr">
+        <is>
+          <t>нет</t>
+        </is>
+      </c>
+      <c r="J60" t="inlineStr">
+        <is>
+          <t>Позитив</t>
+        </is>
+      </c>
+      <c r="K60" t="inlineStr">
+        <is>
+          <t>Нет</t>
+        </is>
+      </c>
+      <c r="L60" t="inlineStr">
+        <is>
+          <t>Медленная</t>
+        </is>
+      </c>
+      <c r="M60" t="inlineStr">
+        <is>
+          <t>Нет возврата</t>
+        </is>
+      </c>
+      <c r="N60" t="inlineStr">
+        <is>
+          <t>Нет</t>
+        </is>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" t="n">
+        <v>1628</v>
+      </c>
+      <c r="B61" t="inlineStr">
+        <is>
+          <t xml:space="preserve">МЕБЕЛЬНЫЙ ДВОР </t>
+        </is>
+      </c>
+      <c r="C61" t="inlineStr">
+        <is>
+          <t>1.0</t>
+        </is>
+      </c>
+      <c r="D61" t="inlineStr">
+        <is>
+          <t>Прошу администрацию обратить внимание на менеджера Екатерину, которая плохо справляется со своей работой. По пунктам 9 ноября купила кухню в Мебельный двор(автовокзал), девушка по имени Екатерина нам её нарисовала и посчитала. Хранилась наша кухня 1 месяц на их складе бесплатно, 28 декабря позвонила, чтобы заказать доставку и мне новость у вас отсутствует 1 фасад. Говорят ждите до 22 января этот один фасад, ладно не приятно но ок подожду. Привезли мне кухню 29 декабря, наняла мастеров начали собирать не хватает ещё корпуса. Звоню в магазин, говорят мне его вообще не поставили в счёт. Ладно ок, ставьте мне в бронь куплю его и заберу со склада. Оплату попросила сделать переводом на карту, чтобы не ехать в магазин. И здесь была моя ошибка, перевела Екатерине не на тот банк. А эта особа вся в долгах как в шелках, карту её арестовали приставы. Итог денег мои ушли в гору и Екатерина отказала их вернуть. Екатерина неосновательно обогатилась за счёт другого человека. Екатерина, надеюсь я этими 2150 хоть чуть чуть покрыла ваши долги....</t>
+        </is>
+      </c>
+      <c r="E61" t="inlineStr">
+        <is>
+          <t>негатив</t>
+        </is>
+      </c>
+      <c r="F61" t="inlineStr">
+        <is>
+          <t>сервис</t>
+        </is>
+      </c>
+      <c r="G61" t="inlineStr">
+        <is>
+          <t>медленная</t>
+        </is>
+      </c>
+      <c r="H61" t="inlineStr">
+        <is>
+          <t>нет возврата</t>
+        </is>
+      </c>
+      <c r="I61" t="inlineStr">
+        <is>
+          <t>корпусная</t>
+        </is>
+      </c>
+      <c r="J61" t="inlineStr">
+        <is>
+          <t>Негатив</t>
+        </is>
+      </c>
+      <c r="K61" t="inlineStr">
+        <is>
+          <t>Сервис</t>
+        </is>
+      </c>
+      <c r="L61" t="inlineStr">
+        <is>
+          <t>Нет</t>
+        </is>
+      </c>
+      <c r="M61" t="inlineStr">
+        <is>
+          <t>Другое</t>
+        </is>
+      </c>
+      <c r="N61" t="inlineStr">
+        <is>
+          <t>Корпусная</t>
+        </is>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" t="n">
+        <v>646</v>
+      </c>
+      <c r="B62" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Москва </t>
+        </is>
+      </c>
+      <c r="C62" t="inlineStr">
+        <is>
+          <t>5.0</t>
+        </is>
+      </c>
+      <c r="D62" t="inlineStr">
+        <is>
+          <t>Недавно выбирала диван и объехала несколько мебельных салонов. Скажу честно, в Москву было заходить страшновато. Вокруг всё, как после бомбежки. Но внутри (если не спускаться в цоколь) всё очень даже достойно. Особенно порадовал выбор и работа продавцов в Мире Мебели. Диван приобрела именно у них, т.к. лучшего выбора цена-качество в городе просто не увидела.</t>
+        </is>
+      </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>негатив</t>
+          <t>позитив</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>сервис</t>
+          <t>нет</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
@@ -4516,17 +4740,17 @@
       </c>
       <c r="I62" t="inlineStr">
         <is>
-          <t>нет</t>
+          <t>мягкая</t>
         </is>
       </c>
       <c r="J62" t="inlineStr">
         <is>
-          <t>Негатив</t>
+          <t>Позитив</t>
         </is>
       </c>
       <c r="K62" t="inlineStr">
         <is>
-          <t>Сервис</t>
+          <t>Нет</t>
         </is>
       </c>
       <c r="L62" t="inlineStr">
@@ -4541,42 +4765,42 @@
       </c>
       <c r="N62" t="inlineStr">
         <is>
-          <t>Корпусная</t>
+          <t>Мягкая</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>10274</v>
+        <v>2439</v>
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>Добрыня</t>
+          <t xml:space="preserve">Мебель vita </t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>5.0</t>
+          <t>1.0</t>
         </is>
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>Мне очень понравился этот магазин, доставили диван через час, консультант была очень доброй и отзывчивой девушкой. К сожалению, не помню, как её зовут</t>
+          <t>Если Вы хотите непродуманную мебель из некачественных материалов, да ещё и чтоб монтажники были с глубокого похмелья, так, чтоб окна приходилось открывать и чтоб «косяки» фирма исправляла очень неохотно, то Вам, конечно, в мебель Вита.</t>
         </is>
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>позитив</t>
+          <t>негатив</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>нет</t>
+          <t>качество</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>быстрая</t>
+          <t>нет</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
@@ -4586,22 +4810,22 @@
       </c>
       <c r="I63" t="inlineStr">
         <is>
-          <t>мягкая</t>
+          <t>нет</t>
         </is>
       </c>
       <c r="J63" t="inlineStr">
         <is>
-          <t>Позитив</t>
+          <t>Негатив</t>
         </is>
       </c>
       <c r="K63" t="inlineStr">
         <is>
-          <t>Нет</t>
+          <t>Качество</t>
         </is>
       </c>
       <c r="L63" t="inlineStr">
         <is>
-          <t>Быстрая</t>
+          <t>Нет</t>
         </is>
       </c>
       <c r="M63" t="inlineStr">
@@ -4611,37 +4835,37 @@
       </c>
       <c r="N63" t="inlineStr">
         <is>
-          <t>Мягкая</t>
+          <t>Нет</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>6155</v>
+        <v>8876</v>
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t xml:space="preserve">Эргомаркет </t>
+          <t>Столплит</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>5.0</t>
+          <t>3.0</t>
         </is>
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>Прекрасный магазин с огромным выбором ортопедической обуви для детей. Купили правильную обувь, цена вполне устроила</t>
+          <t>Качество мебели среднее, но ценник приемлем, если покупать то с осторожностью и не мебель которую будете часто практиковать в быту</t>
         </is>
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>позитив</t>
+          <t>негатив</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>нет</t>
+          <t>качество</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
@@ -4661,12 +4885,12 @@
       </c>
       <c r="J64" t="inlineStr">
         <is>
-          <t>Позитив</t>
+          <t>Нейтрально</t>
         </is>
       </c>
       <c r="K64" t="inlineStr">
         <is>
-          <t>Нет</t>
+          <t>Качество</t>
         </is>
       </c>
       <c r="L64" t="inlineStr">
@@ -4687,21 +4911,21 @@
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>7503</v>
+        <v>634</v>
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t xml:space="preserve">Dizara </t>
+          <t xml:space="preserve">Мира </t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>4.0</t>
+          <t>5.0</t>
         </is>
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>В целом все хорошо, немного затянули по срокам, но главное что мебель без дефектов и по размерам все как надо. Саму установку произвели быстро</t>
+          <t>Хотим оставить положительный отзыв команде и отдельно дизайнеру красивой девушке Александре. Спасибо за кухню😊 грамотный дизайнер и отличная команда!!! Всем рекомендую!! Все в сроки и красиво!!!</t>
         </is>
       </c>
       <c r="E65" t="inlineStr">
@@ -4726,7 +4950,7 @@
       </c>
       <c r="I65" t="inlineStr">
         <is>
-          <t>нет</t>
+          <t>корпусная</t>
         </is>
       </c>
       <c r="J65" t="inlineStr">
@@ -4741,7 +4965,7 @@
       </c>
       <c r="L65" t="inlineStr">
         <is>
-          <t>Медленная</t>
+          <t>Нет</t>
         </is>
       </c>
       <c r="M65" t="inlineStr">
@@ -4751,42 +4975,42 @@
       </c>
       <c r="N65" t="inlineStr">
         <is>
-          <t>Нет</t>
+          <t>Корпусная</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>1628</v>
+        <v>3691</v>
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t xml:space="preserve">МЕБЕЛЬНЫЙ ДВОР </t>
+          <t xml:space="preserve">КанцЛидер </t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>1.0</t>
+          <t>4.0</t>
         </is>
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>Прошу администрацию обратить внимание на менеджера Екатерину, которая плохо справляется со своей работой. По пунктам 9 ноября купила кухню в Мебельный двор(автовокзал), девушка по имени Екатерина нам её нарисовала и посчитала. Хранилась наша кухня 1 месяц на их складе бесплатно, 28 декабря позвонила, чтобы заказать доставку и мне новость у вас отсутствует 1 фасад. Говорят ждите до 22 января этот один фасад, ладно не приятно но ок подожду. Привезли мне кухню 29 декабря, наняла мастеров начали собирать не хватает ещё корпуса. Звоню в магазин, говорят мне его вообще не поставили в счёт. Ладно ок, ставьте мне в бронь куплю его и заберу со склада. Оплату попросила сделать переводом на карту, чтобы не ехать в магазин. И здесь была моя ошибка, перевела Екатерине не на тот банк. А эта особа вся в долгах как в шелках, карту её арестовали приставы. Итог денег мои ушли в гору и Екатерина отказала их вернуть. Екатерина неосновательно обогатилась за счёт другого человека. Екатерина, надеюсь я этими 2150 хоть чуть чуть покрыла ваши долги....</t>
+          <t>Хороший магазин, качественная канцелярия. Правда, не предупреждают о доставке, приезжают наобум, пришлось приехать два раза.</t>
         </is>
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>негатив</t>
+          <t>нейтрально</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>сервис</t>
+          <t>нет</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>медленная</t>
+          <t>нет</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
@@ -4796,12 +5020,12 @@
       </c>
       <c r="I66" t="inlineStr">
         <is>
-          <t>корпусная</t>
+          <t>нет</t>
         </is>
       </c>
       <c r="J66" t="inlineStr">
         <is>
-          <t>Негатив</t>
+          <t>Нейтрально</t>
         </is>
       </c>
       <c r="K66" t="inlineStr">
@@ -4816,22 +5040,22 @@
       </c>
       <c r="M66" t="inlineStr">
         <is>
-          <t>Другое</t>
+          <t>Нет возврата</t>
         </is>
       </c>
       <c r="N66" t="inlineStr">
         <is>
-          <t>Корпусная</t>
+          <t>Нет</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>646</v>
+        <v>316</v>
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t xml:space="preserve">Москва </t>
+          <t xml:space="preserve">Столплит </t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
@@ -4841,7 +5065,7 @@
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>Недавно выбирала диван и объехала несколько мебельных салонов. Скажу честно, в Москву было заходить страшновато. Вокруг всё, как после бомбежки. Но внутри (если не спускаться в цоколь) всё очень даже достойно. Особенно порадовал выбор и работа продавцов в Мире Мебели. Диван приобрела именно у них, т.к. лучшего выбора цена-качество в городе просто не увидела.</t>
+          <t>Купили шкаф. На самом деле очень долго искали подходящий вариант. Не устраивала или цена, или цвет, или доставка. Здесь подошло все. Консультанты отличные, помогли подобрать подходящий вариант. Цены вообще на всю мебель приемлемые.</t>
         </is>
       </c>
       <c r="E67" t="inlineStr">
@@ -4866,7 +5090,7 @@
       </c>
       <c r="I67" t="inlineStr">
         <is>
-          <t>мягкая</t>
+          <t>корпусная</t>
         </is>
       </c>
       <c r="J67" t="inlineStr">
@@ -4891,63 +5115,107 @@
       </c>
       <c r="N67" t="inlineStr">
         <is>
-          <t>Мягкая</t>
+          <t>Корпусная</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>10851</v>
+        <v>4231</v>
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>Октябрьский</t>
+          <t xml:space="preserve">Адель </t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>5 звезд</t>
-        </is>
-      </c>
-      <c r="D68" t="inlineStr"/>
-      <c r="E68" t="inlineStr"/>
-      <c r="F68" t="inlineStr"/>
-      <c r="G68" t="inlineStr"/>
-      <c r="H68" t="inlineStr"/>
-      <c r="I68" t="inlineStr"/>
-      <c r="J68" t="inlineStr"/>
-      <c r="K68" t="inlineStr"/>
-      <c r="L68" t="inlineStr"/>
-      <c r="M68" t="inlineStr"/>
-      <c r="N68" t="inlineStr"/>
+          <t>5.0</t>
+        </is>
+      </c>
+      <c r="D68" t="inlineStr">
+        <is>
+          <t>Отличный магазин с которого никогда не уйдешь без покупки! Огромный ассортимент, представлено много товаров ИКЕА. Всегда внимательное обслуживание и гибкая система скидок! Успеха вам!</t>
+        </is>
+      </c>
+      <c r="E68" t="inlineStr">
+        <is>
+          <t>позитив</t>
+        </is>
+      </c>
+      <c r="F68" t="inlineStr">
+        <is>
+          <t>нет</t>
+        </is>
+      </c>
+      <c r="G68" t="inlineStr">
+        <is>
+          <t>нет</t>
+        </is>
+      </c>
+      <c r="H68" t="inlineStr">
+        <is>
+          <t>нет возврата</t>
+        </is>
+      </c>
+      <c r="I68" t="inlineStr">
+        <is>
+          <t>нет</t>
+        </is>
+      </c>
+      <c r="J68" t="inlineStr">
+        <is>
+          <t>Позитив</t>
+        </is>
+      </c>
+      <c r="K68" t="inlineStr">
+        <is>
+          <t>Нет</t>
+        </is>
+      </c>
+      <c r="L68" t="inlineStr">
+        <is>
+          <t>Нет</t>
+        </is>
+      </c>
+      <c r="M68" t="inlineStr">
+        <is>
+          <t>Нет возврата</t>
+        </is>
+      </c>
+      <c r="N68" t="inlineStr">
+        <is>
+          <t>Нет</t>
+        </is>
+      </c>
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>2439</v>
+        <v>721</v>
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t xml:space="preserve">Мебель vita </t>
+          <t xml:space="preserve">Октябрьский </t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>1.0</t>
+          <t>5.0</t>
         </is>
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>Если Вы хотите непродуманную мебель из некачественных материалов, да ещё и чтоб монтажники были с глубокого похмелья, так, чтоб окна приходилось открывать и чтоб «косяки» фирма исправляла очень неохотно, то Вам, конечно, в мебель Вита.</t>
+          <t>Fix price one luv:333</t>
         </is>
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>негатив</t>
+          <t>нейтрально</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>качество</t>
+          <t>нет</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
@@ -4967,12 +5235,12 @@
       </c>
       <c r="J69" t="inlineStr">
         <is>
-          <t>Негатив</t>
+          <t>Нейтрально</t>
         </is>
       </c>
       <c r="K69" t="inlineStr">
         <is>
-          <t>Качество</t>
+          <t>Иное</t>
         </is>
       </c>
       <c r="L69" t="inlineStr">
@@ -4993,31 +5261,31 @@
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>8876</v>
+        <v>6030</v>
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>Столплит</t>
+          <t xml:space="preserve">Мир мебели </t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>3.0</t>
+          <t>5.0</t>
         </is>
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>Качество мебели среднее, но ценник приемлем, если покупать то с осторожностью и не мебель которую будете часто практиковать в быту</t>
+          <t>Делаем ремонт. Заказали здесь мебель от Дятьково. Ждем с нетерпением нашу новую спальню и прихожую. Планируем вернуться за детской через год</t>
         </is>
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>негатив</t>
+          <t>позитив</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>качество</t>
+          <t>нет</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
@@ -5032,17 +5300,17 @@
       </c>
       <c r="I70" t="inlineStr">
         <is>
-          <t>нет</t>
+          <t>корпусная</t>
         </is>
       </c>
       <c r="J70" t="inlineStr">
         <is>
-          <t>Нейтрально</t>
+          <t>Позитив</t>
         </is>
       </c>
       <c r="K70" t="inlineStr">
         <is>
-          <t>Качество</t>
+          <t>Нет</t>
         </is>
       </c>
       <c r="L70" t="inlineStr">
@@ -5057,17 +5325,17 @@
       </c>
       <c r="N70" t="inlineStr">
         <is>
-          <t>Нет</t>
+          <t>Корпусная</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>634</v>
+        <v>8729</v>
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t xml:space="preserve">Мира </t>
+          <t>Бабр</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
@@ -5077,7 +5345,7 @@
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>Хотим оставить положительный отзыв команде и отдельно дизайнеру красивой девушке Александре. Спасибо за кухню😊 грамотный дизайнер и отличная команда!!! Всем рекомендую!! Все в сроки и красиво!!!</t>
+          <t>Отличный магазин! Помогли подобрать мебель в детскую комнату, проконсультировали от и до. Цена тоже радует, качество на высоте. Рекомендую! Сделали все под ключ, с доставкой и сборкой.</t>
         </is>
       </c>
       <c r="E71" t="inlineStr">
@@ -5092,7 +5360,7 @@
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>быстрая</t>
+          <t>нет</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
@@ -5133,21 +5401,21 @@
     </row>
     <row r="72">
       <c r="A72" t="n">
-        <v>3691</v>
+        <v>10916</v>
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t xml:space="preserve">КанцЛидер </t>
+          <t>Атриум, сеть мебельных центров</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>4.0</t>
+          <t>4 звезды</t>
         </is>
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>Хороший магазин, качественная канцелярия. Правда, не предупреждают о доставке, приезжают наобум, пришлось приехать два раза.</t>
+          <t>Цена качество,в принципе на твердую четверку.А вот доставка-печально."Догоняли" свою мебель больше месяца ((</t>
         </is>
       </c>
       <c r="E72" t="inlineStr">
@@ -5162,7 +5430,7 @@
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>нет</t>
+          <t>медленная</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
@@ -5187,7 +5455,7 @@
       </c>
       <c r="L72" t="inlineStr">
         <is>
-          <t>Нет</t>
+          <t>Медленная</t>
         </is>
       </c>
       <c r="M72" t="inlineStr">
@@ -5203,31 +5471,32 @@
     </row>
     <row r="73">
       <c r="A73" t="n">
-        <v>316</v>
+        <v>6607</v>
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t xml:space="preserve">Столплит </t>
+          <t xml:space="preserve">Мебель центр </t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>5.0</t>
+          <t>1.0</t>
         </is>
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t>Купили шкаф. На самом деле очень долго искали подходящий вариант. Не устраивала или цена, или цвет, или доставка. Здесь подошло все. Консультанты отличные, помогли подобрать подходящий вариант. Цены вообще на всю мебель приемлемые.</t>
+          <t>Отношение консультантов ужасное, будто за их счет покупаю.🤦‍♀️
+Все недовольство показали нам🤦‍♀️</t>
         </is>
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>позитив</t>
+          <t>негатив</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>нет</t>
+          <t>сервис</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
@@ -5242,17 +5511,17 @@
       </c>
       <c r="I73" t="inlineStr">
         <is>
-          <t>корпусная</t>
+          <t>нет</t>
         </is>
       </c>
       <c r="J73" t="inlineStr">
         <is>
-          <t>Позитив</t>
+          <t>Негатив</t>
         </is>
       </c>
       <c r="K73" t="inlineStr">
         <is>
-          <t>Нет</t>
+          <t>Сервис</t>
         </is>
       </c>
       <c r="L73" t="inlineStr">
@@ -5267,39 +5536,87 @@
       </c>
       <c r="N73" t="inlineStr">
         <is>
-          <t>Корпусная</t>
+          <t>Нет</t>
         </is>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="n">
-        <v>3448</v>
+        <v>10795</v>
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t xml:space="preserve">Шатура </t>
-        </is>
-      </c>
-      <c r="C74" t="inlineStr"/>
-      <c r="D74" t="inlineStr"/>
-      <c r="E74" t="inlineStr"/>
-      <c r="F74" t="inlineStr"/>
-      <c r="G74" t="inlineStr"/>
-      <c r="H74" t="inlineStr"/>
-      <c r="I74" t="inlineStr"/>
-      <c r="J74" t="inlineStr"/>
-      <c r="K74" t="inlineStr"/>
-      <c r="L74" t="inlineStr"/>
-      <c r="M74" t="inlineStr"/>
-      <c r="N74" t="inlineStr"/>
+          <t>Октябрьский</t>
+        </is>
+      </c>
+      <c r="C74" t="inlineStr">
+        <is>
+          <t>4 звезды</t>
+        </is>
+      </c>
+      <c r="D74" t="inlineStr">
+        <is>
+          <t>Много разной мебели?</t>
+        </is>
+      </c>
+      <c r="E74" t="inlineStr">
+        <is>
+          <t>нейтрально</t>
+        </is>
+      </c>
+      <c r="F74" t="inlineStr">
+        <is>
+          <t>нет</t>
+        </is>
+      </c>
+      <c r="G74" t="inlineStr">
+        <is>
+          <t>нет</t>
+        </is>
+      </c>
+      <c r="H74" t="inlineStr">
+        <is>
+          <t>нет возврата</t>
+        </is>
+      </c>
+      <c r="I74" t="inlineStr">
+        <is>
+          <t>нет</t>
+        </is>
+      </c>
+      <c r="J74" t="inlineStr">
+        <is>
+          <t>Нейтрально</t>
+        </is>
+      </c>
+      <c r="K74" t="inlineStr">
+        <is>
+          <t>Иное</t>
+        </is>
+      </c>
+      <c r="L74" t="inlineStr">
+        <is>
+          <t>Нет</t>
+        </is>
+      </c>
+      <c r="M74" t="inlineStr">
+        <is>
+          <t>Нет возврата</t>
+        </is>
+      </c>
+      <c r="N74" t="inlineStr">
+        <is>
+          <t>Нет</t>
+        </is>
+      </c>
     </row>
     <row r="75">
       <c r="A75" t="n">
-        <v>4231</v>
+        <v>134</v>
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t xml:space="preserve">Адель </t>
+          <t xml:space="preserve">Марина </t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
@@ -5309,12 +5626,12 @@
       </c>
       <c r="D75" t="inlineStr">
         <is>
-          <t>Отличный магазин с которого никогда не уйдешь без покупки! Огромный ассортимент, представлено много товаров ИКЕА. Всегда внимательное обслуживание и гибкая система скидок! Успеха вам!</t>
+          <t>Низкие цены. Неплохое качество.</t>
         </is>
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>позитив</t>
+          <t>нейтрально</t>
         </is>
       </c>
       <c r="F75" t="inlineStr">
@@ -5365,11 +5682,11 @@
     </row>
     <row r="76">
       <c r="A76" t="n">
-        <v>721</v>
+        <v>9789</v>
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t xml:space="preserve">Октябрьский </t>
+          <t>АМТ</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
@@ -5379,12 +5696,12 @@
       </c>
       <c r="D76" t="inlineStr">
         <is>
-          <t>Fix price one luv:333</t>
+          <t>Классный магазин.</t>
         </is>
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>нейтрально</t>
+          <t>позитив</t>
         </is>
       </c>
       <c r="F76" t="inlineStr">
@@ -5409,12 +5726,12 @@
       </c>
       <c r="J76" t="inlineStr">
         <is>
-          <t>Нейтрально</t>
+          <t>Позитив</t>
         </is>
       </c>
       <c r="K76" t="inlineStr">
         <is>
-          <t>Иное</t>
+          <t>Нет</t>
         </is>
       </c>
       <c r="L76" t="inlineStr">
@@ -5435,11 +5752,11 @@
     </row>
     <row r="77">
       <c r="A77" t="n">
-        <v>6030</v>
+        <v>859</v>
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t xml:space="preserve">Мир мебели </t>
+          <t xml:space="preserve">Askona </t>
         </is>
       </c>
       <c r="C77" t="inlineStr">
@@ -5449,7 +5766,7 @@
       </c>
       <c r="D77" t="inlineStr">
         <is>
-          <t>Делаем ремонт. Заказали здесь мебель от Дятьково. Ждем с нетерпением нашу новую спальню и прихожую. Планируем вернуться за детской через год</t>
+          <t>Приобретала матрас в ТЦ Адмирал.Очень понравилась квалифицированная консультация Константина и Екатерины,подобрали мне отличный матрас.Доставочку сделали сразу на следующий день ,как и пообещели. Очень довольна, Рекомендую этот салон!!!</t>
         </is>
       </c>
       <c r="E77" t="inlineStr">
@@ -5474,7 +5791,7 @@
       </c>
       <c r="I77" t="inlineStr">
         <is>
-          <t>корпусная</t>
+          <t>мягкая</t>
         </is>
       </c>
       <c r="J77" t="inlineStr">
@@ -5489,7 +5806,7 @@
       </c>
       <c r="L77" t="inlineStr">
         <is>
-          <t>Нет</t>
+          <t>Быстрая</t>
         </is>
       </c>
       <c r="M77" t="inlineStr">
@@ -5499,17 +5816,17 @@
       </c>
       <c r="N77" t="inlineStr">
         <is>
-          <t>Корпусная</t>
+          <t>Нет</t>
         </is>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="n">
-        <v>8729</v>
+        <v>2258</v>
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>Бабр</t>
+          <t xml:space="preserve">DaVita </t>
         </is>
       </c>
       <c r="C78" t="inlineStr">
@@ -5519,7 +5836,7 @@
       </c>
       <c r="D78" t="inlineStr">
         <is>
-          <t>Отличный магазин! Помогли подобрать мебель в детскую комнату, проконсультировали от и до. Цена тоже радует, качество на высоте. Рекомендую! Сделали все под ключ, с доставкой и сборкой.</t>
+          <t>Сначала сомневались, так как цены выше среднего, но когда начали открывать дверки и увидели достаточно дорогую фурнитуру, сомнением уже не было. Девушка помогла нам в выбором, объяснила как делать замеры, предложила помощь замерщика. Мы оплатили и нам бесплатно привезли и собрали кухню, пользуемся больше месяца, никаких нареканий нет.</t>
         </is>
       </c>
       <c r="E78" t="inlineStr">
@@ -5559,7 +5876,7 @@
       </c>
       <c r="L78" t="inlineStr">
         <is>
-          <t>Нет</t>
+          <t>Быстрая</t>
         </is>
       </c>
       <c r="M78" t="inlineStr">
@@ -5575,26 +5892,26 @@
     </row>
     <row r="79">
       <c r="A79" t="n">
-        <v>10916</v>
+        <v>3433</v>
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>Атриум, сеть мебельных центров</t>
+          <t xml:space="preserve">Фартовый </t>
         </is>
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>4 звезды</t>
+          <t>5.0</t>
         </is>
       </c>
       <c r="D79" t="inlineStr">
         <is>
-          <t>Цена качество,в принципе на твердую четверку.А вот доставка-печально."Догоняли" свою мебель больше месяца ((</t>
+          <t>огромное спасибо продавцам не первый раз покупаем в этом магазине, и продавцы всегда внимательные спокойные и не смотрят на тебя с высока. Да сборщикам мебели вы супер быстрые мастера))))</t>
         </is>
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>нейтрально</t>
+          <t>позитив</t>
         </is>
       </c>
       <c r="F79" t="inlineStr">
@@ -5604,7 +5921,7 @@
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>медленная</t>
+          <t>нет</t>
         </is>
       </c>
       <c r="H79" t="inlineStr">
@@ -5619,17 +5936,17 @@
       </c>
       <c r="J79" t="inlineStr">
         <is>
-          <t>Нейтрально</t>
+          <t>Позитив</t>
         </is>
       </c>
       <c r="K79" t="inlineStr">
         <is>
-          <t>Сервис</t>
+          <t>Нет</t>
         </is>
       </c>
       <c r="L79" t="inlineStr">
         <is>
-          <t>Медленная</t>
+          <t>Нет</t>
         </is>
       </c>
       <c r="M79" t="inlineStr">
@@ -5645,32 +5962,31 @@
     </row>
     <row r="80">
       <c r="A80" t="n">
-        <v>6607</v>
+        <v>2179</v>
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t xml:space="preserve">Мебель центр </t>
+          <t xml:space="preserve">Ваш уют </t>
         </is>
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>1.0</t>
+          <t>5.0</t>
         </is>
       </c>
       <c r="D80" t="inlineStr">
         <is>
-          <t>Отношение консультантов ужасное, будто за их счет покупаю.🤦‍♀️
-Все недовольство показали нам🤦‍♀️</t>
+          <t>Заказывали шкаф, кровать и тумбочку в данном салоне, понравилось все от консультации до установки. Мебель получилась классная, современная, мы остались очень довольны. Спасибо менеджеру Анне и салону «Ваш уют» за внимательность и высокий профессионализм!</t>
         </is>
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>негатив</t>
+          <t>позитив</t>
         </is>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>сервис</t>
+          <t>нет</t>
         </is>
       </c>
       <c r="G80" t="inlineStr">
@@ -5685,17 +6001,17 @@
       </c>
       <c r="I80" t="inlineStr">
         <is>
-          <t>нет</t>
+          <t>корпусная</t>
         </is>
       </c>
       <c r="J80" t="inlineStr">
         <is>
-          <t>Негатив</t>
+          <t>Позитив</t>
         </is>
       </c>
       <c r="K80" t="inlineStr">
         <is>
-          <t>Сервис</t>
+          <t>Нет</t>
         </is>
       </c>
       <c r="L80" t="inlineStr">
@@ -5710,32 +6026,32 @@
       </c>
       <c r="N80" t="inlineStr">
         <is>
-          <t>Нет</t>
+          <t>Корпусная</t>
         </is>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="n">
-        <v>10795</v>
+        <v>11077</v>
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>Октябрьский</t>
+          <t>Мир мебели</t>
         </is>
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>4 звезды</t>
+          <t>5 звезд</t>
         </is>
       </c>
       <c r="D81" t="inlineStr">
         <is>
-          <t>Много разной мебели?</t>
+          <t>Покупали комод и книжный шкаф фирмы Дятьково. В общем-то, подобрали себе всё сами и по цвету, и по форме, но, как говорится, хозяин - барин. Консультант тоже старалась, но безуспешно) Организовали всё быстро: оформили оплату, доставку. …</t>
         </is>
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>нейтрально</t>
+          <t>позитив</t>
         </is>
       </c>
       <c r="F81" t="inlineStr">
@@ -5760,17 +6076,17 @@
       </c>
       <c r="J81" t="inlineStr">
         <is>
-          <t>Нейтрально</t>
+          <t>Позитив</t>
         </is>
       </c>
       <c r="K81" t="inlineStr">
         <is>
-          <t>Иное</t>
+          <t>Нет</t>
         </is>
       </c>
       <c r="L81" t="inlineStr">
         <is>
-          <t>Нет</t>
+          <t>Быстрая</t>
         </is>
       </c>
       <c r="M81" t="inlineStr">
@@ -5780,43 +6096,87 @@
       </c>
       <c r="N81" t="inlineStr">
         <is>
-          <t>Нет</t>
+          <t>Корпусная</t>
         </is>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="n">
-        <v>11655</v>
+        <v>8077</v>
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>ДОМ, салон мебели</t>
+          <t xml:space="preserve">Профессионал М </t>
         </is>
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>5 звезд</t>
-        </is>
-      </c>
-      <c r="D82" t="inlineStr"/>
-      <c r="E82" t="inlineStr"/>
-      <c r="F82" t="inlineStr"/>
-      <c r="G82" t="inlineStr"/>
-      <c r="H82" t="inlineStr"/>
-      <c r="I82" t="inlineStr"/>
-      <c r="J82" t="inlineStr"/>
-      <c r="K82" t="inlineStr"/>
-      <c r="L82" t="inlineStr"/>
-      <c r="M82" t="inlineStr"/>
-      <c r="N82" t="inlineStr"/>
+          <t>1.0</t>
+        </is>
+      </c>
+      <c r="D82" t="inlineStr">
+        <is>
+          <t>Отвратительное качество товара. Купили диван, сделали все с нуля на заказ. Через месяц уже появился ужасно сильный скрип.</t>
+        </is>
+      </c>
+      <c r="E82" t="inlineStr">
+        <is>
+          <t>негатив</t>
+        </is>
+      </c>
+      <c r="F82" t="inlineStr">
+        <is>
+          <t>качество</t>
+        </is>
+      </c>
+      <c r="G82" t="inlineStr">
+        <is>
+          <t>нет</t>
+        </is>
+      </c>
+      <c r="H82" t="inlineStr">
+        <is>
+          <t>нет возврата</t>
+        </is>
+      </c>
+      <c r="I82" t="inlineStr">
+        <is>
+          <t>мягкая</t>
+        </is>
+      </c>
+      <c r="J82" t="inlineStr">
+        <is>
+          <t>Негатив</t>
+        </is>
+      </c>
+      <c r="K82" t="inlineStr">
+        <is>
+          <t>Качество</t>
+        </is>
+      </c>
+      <c r="L82" t="inlineStr">
+        <is>
+          <t>Нет</t>
+        </is>
+      </c>
+      <c r="M82" t="inlineStr">
+        <is>
+          <t>Брак</t>
+        </is>
+      </c>
+      <c r="N82" t="inlineStr">
+        <is>
+          <t>Мягкая</t>
+        </is>
+      </c>
     </row>
     <row r="83">
       <c r="A83" t="n">
-        <v>134</v>
+        <v>2080</v>
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t xml:space="preserve">Марина </t>
+          <t xml:space="preserve">Cucina.Studio </t>
         </is>
       </c>
       <c r="C83" t="inlineStr">
@@ -5826,12 +6186,12 @@
       </c>
       <c r="D83" t="inlineStr">
         <is>
-          <t>Низкие цены. Неплохое качество.</t>
+          <t>Спасибо кoмпании за нашу нoвую кухню! Все быстро в срoк, качество на высoте, а самoе главнoе сборка заняла всего oдин день. Oчень благoдарны Вам за вашу рабoту!</t>
         </is>
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>нейтрально</t>
+          <t>позитив</t>
         </is>
       </c>
       <c r="F83" t="inlineStr">
@@ -5841,7 +6201,7 @@
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>нет</t>
+          <t>быстрая</t>
         </is>
       </c>
       <c r="H83" t="inlineStr">
@@ -5851,7 +6211,7 @@
       </c>
       <c r="I83" t="inlineStr">
         <is>
-          <t>нет</t>
+          <t>корпусная</t>
         </is>
       </c>
       <c r="J83" t="inlineStr">
@@ -5866,7 +6226,7 @@
       </c>
       <c r="L83" t="inlineStr">
         <is>
-          <t>Нет</t>
+          <t>Быстрая</t>
         </is>
       </c>
       <c r="M83" t="inlineStr">
@@ -5876,17 +6236,17 @@
       </c>
       <c r="N83" t="inlineStr">
         <is>
-          <t>Нет</t>
+          <t>Корпусная</t>
         </is>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="n">
-        <v>9789</v>
+        <v>1129</v>
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>АМТ</t>
+          <t xml:space="preserve">Диван38 </t>
         </is>
       </c>
       <c r="C84" t="inlineStr">
@@ -5896,7 +6256,7 @@
       </c>
       <c r="D84" t="inlineStr">
         <is>
-          <t>Классный магазин.</t>
+          <t>Спасибо! Спасибо огромное за то, что даже к такому привередливому покупателю как я, в этом магазине ко мне нашли подход и подобрали нужный размер на заказ, расцветку и даже цвет строчки, сделали все быстро и качественно!</t>
         </is>
       </c>
       <c r="E84" t="inlineStr">
@@ -5911,7 +6271,7 @@
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>нет</t>
+          <t>быстрая</t>
         </is>
       </c>
       <c r="H84" t="inlineStr">
@@ -5936,7 +6296,7 @@
       </c>
       <c r="L84" t="inlineStr">
         <is>
-          <t>Нет</t>
+          <t>Быстрая</t>
         </is>
       </c>
       <c r="M84" t="inlineStr">
@@ -5952,11 +6312,11 @@
     </row>
     <row r="85">
       <c r="A85" t="n">
-        <v>859</v>
+        <v>4624</v>
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t xml:space="preserve">Askona </t>
+          <t xml:space="preserve">#мебельмаркет </t>
         </is>
       </c>
       <c r="C85" t="inlineStr">
@@ -5966,7 +6326,7 @@
       </c>
       <c r="D85" t="inlineStr">
         <is>
-          <t>Приобретала матрас в ТЦ Адмирал.Очень понравилась квалифицированная консультация Константина и Екатерины,подобрали мне отличный матрас.Доставочку сделали сразу на следующий день ,как и пообещели. Очень довольна, Рекомендую этот салон!!!</t>
+          <t>Очень довольна заказанным у вас диваном! Идеально подошел по размерам и цвету, доставили в тот же день, а сборка прошла быстро и без проблем. Спасибо за высокое качество и доступные цены!</t>
         </is>
       </c>
       <c r="E85" t="inlineStr">
@@ -6016,37 +6376,38 @@
       </c>
       <c r="N85" t="inlineStr">
         <is>
-          <t>Нет</t>
+          <t>Мягкая</t>
         </is>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="n">
-        <v>2258</v>
+        <v>8268</v>
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t xml:space="preserve">DaVita </t>
+          <t xml:space="preserve">Мебель хит </t>
         </is>
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>5.0</t>
+          <t>1.0</t>
         </is>
       </c>
       <c r="D86" t="inlineStr">
         <is>
-          <t>Сначала сомневались, так как цены выше среднего, но когда начали открывать дверки и увидели достаточно дорогую фурнитуру, сомнением уже не было. Девушка помогла нам в выбором, объяснила как делать замеры, предложила помощь замерщика. Мы оплатили и нам бесплатно привезли и собрали кухню, пользуемся больше месяца, никаких нареканий нет.</t>
+          <t>Ужасная организация! Заказываешь одно, по факту получаешь другое. Цены меняют на глазах! Оформлять заказы на мебель не научились. Никакой клиентоориентированности. Жалко потраченное время и нервы.
+Больше ни ногой.</t>
         </is>
       </c>
       <c r="E86" t="inlineStr">
         <is>
-          <t>позитив</t>
+          <t>негатив</t>
         </is>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>нет</t>
+          <t>сервис</t>
         </is>
       </c>
       <c r="G86" t="inlineStr">
@@ -6061,42 +6422,42 @@
       </c>
       <c r="I86" t="inlineStr">
         <is>
-          <t>корпусная</t>
+          <t>нет</t>
         </is>
       </c>
       <c r="J86" t="inlineStr">
         <is>
-          <t>Позитив</t>
+          <t>Негатив</t>
         </is>
       </c>
       <c r="K86" t="inlineStr">
         <is>
-          <t>Нет</t>
+          <t>Сервис</t>
         </is>
       </c>
       <c r="L86" t="inlineStr">
         <is>
-          <t>Быстрая</t>
+          <t>Нет</t>
         </is>
       </c>
       <c r="M86" t="inlineStr">
         <is>
-          <t>Нет возврата</t>
+          <t>Несоответствие описанию</t>
         </is>
       </c>
       <c r="N86" t="inlineStr">
         <is>
-          <t>Корпусная</t>
+          <t>Нет</t>
         </is>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="n">
-        <v>3433</v>
+        <v>7812</v>
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t xml:space="preserve">Фартовый </t>
+          <t xml:space="preserve">Виктория </t>
         </is>
       </c>
       <c r="C87" t="inlineStr">
@@ -6106,7 +6467,7 @@
       </c>
       <c r="D87" t="inlineStr">
         <is>
-          <t>огромное спасибо продавцам не первый раз покупаем в этом магазине, и продавцы всегда внимательные спокойные и не смотрят на тебя с высока. Да сборщикам мебели вы супер быстрые мастера))))</t>
+          <t>Хочу сказать большое спасибо мастерам Александру и Ивану за отличную работу, перетяжка дивана выполненна на отлично! Впредь буду обращаться в эту фирму! Выражаю огромную благодарнлсть</t>
         </is>
       </c>
       <c r="E87" t="inlineStr">
@@ -6156,32 +6517,32 @@
       </c>
       <c r="N87" t="inlineStr">
         <is>
-          <t>Нет</t>
+          <t>Мягкая</t>
         </is>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="n">
-        <v>2179</v>
+        <v>12432</v>
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t xml:space="preserve">Ваш уют </t>
+          <t>По щучьему велению!</t>
         </is>
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>5.0</t>
+          <t>4 звезды</t>
         </is>
       </c>
       <c r="D88" t="inlineStr">
         <is>
-          <t>Заказывали шкаф, кровать и тумбочку в данном салоне, понравилось все от консультации до установки. Мебель получилась классная, современная, мы остались очень довольны. Спасибо менеджеру Анне и салону «Ваш уют» за внимательность и высокий профессионализм!</t>
+          <t>Мне нравиться магазин абсолют</t>
         </is>
       </c>
       <c r="E88" t="inlineStr">
         <is>
-          <t>позитив</t>
+          <t>нейтрально</t>
         </is>
       </c>
       <c r="F88" t="inlineStr">
@@ -6201,7 +6562,7 @@
       </c>
       <c r="I88" t="inlineStr">
         <is>
-          <t>корпусная</t>
+          <t>нет</t>
         </is>
       </c>
       <c r="J88" t="inlineStr">
@@ -6226,27 +6587,27 @@
       </c>
       <c r="N88" t="inlineStr">
         <is>
-          <t>Корпусная</t>
+          <t>Нет</t>
         </is>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="n">
-        <v>11077</v>
+        <v>7639</v>
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>Мир мебели</t>
+          <t xml:space="preserve">Алекон </t>
         </is>
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>5 звезд</t>
+          <t>5.0</t>
         </is>
       </c>
       <c r="D89" t="inlineStr">
         <is>
-          <t>Покупали комод и книжный шкаф фирмы Дятьково. В общем-то, подобрали себе всё сами и по цвету, и по форме, но, как говорится, хозяин - барин. Консультант тоже старалась, но безуспешно) Организовали всё быстро: оформили оплату, доставку. …</t>
+          <t>Ребята молодцы все очень красиво и аккуратно</t>
         </is>
       </c>
       <c r="E89" t="inlineStr">
@@ -6286,7 +6647,7 @@
       </c>
       <c r="L89" t="inlineStr">
         <is>
-          <t>Быстрая</t>
+          <t>Нет</t>
         </is>
       </c>
       <c r="M89" t="inlineStr">
@@ -6296,37 +6657,37 @@
       </c>
       <c r="N89" t="inlineStr">
         <is>
-          <t>Корпусная</t>
+          <t>Нет</t>
         </is>
       </c>
     </row>
     <row r="90">
       <c r="A90" t="n">
-        <v>8077</v>
+        <v>12717</v>
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t xml:space="preserve">Профессионал М </t>
+          <t>Атриум, студия детской мебели</t>
         </is>
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>1.0</t>
+          <t>2 звезды</t>
         </is>
       </c>
       <c r="D90" t="inlineStr">
         <is>
-          <t>Отвратительное качество товара. Купили диван, сделали все с нуля на заказ. Через месяц уже появился ужасно сильный скрип.</t>
+          <t>Дорого</t>
         </is>
       </c>
       <c r="E90" t="inlineStr">
         <is>
-          <t>негатив</t>
+          <t>нейтрально</t>
         </is>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>качество</t>
+          <t>нет</t>
         </is>
       </c>
       <c r="G90" t="inlineStr">
@@ -6341,7 +6702,7 @@
       </c>
       <c r="I90" t="inlineStr">
         <is>
-          <t>мягкая</t>
+          <t>нет</t>
         </is>
       </c>
       <c r="J90" t="inlineStr">
@@ -6351,7 +6712,7 @@
       </c>
       <c r="K90" t="inlineStr">
         <is>
-          <t>Качество</t>
+          <t>Иное</t>
         </is>
       </c>
       <c r="L90" t="inlineStr">
@@ -6361,22 +6722,22 @@
       </c>
       <c r="M90" t="inlineStr">
         <is>
-          <t>Брак</t>
+          <t>Нет возврата</t>
         </is>
       </c>
       <c r="N90" t="inlineStr">
         <is>
-          <t>Мягкая</t>
+          <t>Нет</t>
         </is>
       </c>
     </row>
     <row r="91">
       <c r="A91" t="n">
-        <v>2080</v>
+        <v>1351</v>
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t xml:space="preserve">Cucina.Studio </t>
+          <t xml:space="preserve">Nordeagle Mebel </t>
         </is>
       </c>
       <c r="C91" t="inlineStr">
@@ -6386,7 +6747,7 @@
       </c>
       <c r="D91" t="inlineStr">
         <is>
-          <t>Спасибо кoмпании за нашу нoвую кухню! Все быстро в срoк, качество на высoте, а самoе главнoе сборка заняла всего oдин день. Oчень благoдарны Вам за вашу рабoту!</t>
+          <t>Все классно, очень довольны, не смотря на позднюю доставку.</t>
         </is>
       </c>
       <c r="E91" t="inlineStr">
@@ -6401,7 +6762,7 @@
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>быстрая</t>
+          <t>медленная</t>
         </is>
       </c>
       <c r="H91" t="inlineStr">
@@ -6411,7 +6772,7 @@
       </c>
       <c r="I91" t="inlineStr">
         <is>
-          <t>корпусная</t>
+          <t>нет</t>
         </is>
       </c>
       <c r="J91" t="inlineStr">
@@ -6426,7 +6787,7 @@
       </c>
       <c r="L91" t="inlineStr">
         <is>
-          <t>Быстрая</t>
+          <t>Медленная</t>
         </is>
       </c>
       <c r="M91" t="inlineStr">
@@ -6436,586 +6797,25 @@
       </c>
       <c r="N91" t="inlineStr">
         <is>
-          <t>Корпусная</t>
+          <t>Нет</t>
         </is>
       </c>
     </row>
     <row r="92">
       <c r="A92" t="n">
-        <v>1129</v>
+        <v>4749</v>
       </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t xml:space="preserve">Диван38 </t>
+          <t xml:space="preserve">Много Мебели </t>
         </is>
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>5.0</t>
+          <t>3.0</t>
         </is>
       </c>
       <c r="D92" t="inlineStr">
-        <is>
-          <t>Спасибо! Спасибо огромное за то, что даже к такому привередливому покупателю как я, в этом магазине ко мне нашли подход и подобрали нужный размер на заказ, расцветку и даже цвет строчки, сделали все быстро и качественно!</t>
-        </is>
-      </c>
-      <c r="E92" t="inlineStr">
-        <is>
-          <t>позитив</t>
-        </is>
-      </c>
-      <c r="F92" t="inlineStr">
-        <is>
-          <t>нет</t>
-        </is>
-      </c>
-      <c r="G92" t="inlineStr">
-        <is>
-          <t>быстрая</t>
-        </is>
-      </c>
-      <c r="H92" t="inlineStr">
-        <is>
-          <t>нет возврата</t>
-        </is>
-      </c>
-      <c r="I92" t="inlineStr">
-        <is>
-          <t>нет</t>
-        </is>
-      </c>
-      <c r="J92" t="inlineStr">
-        <is>
-          <t>Позитив</t>
-        </is>
-      </c>
-      <c r="K92" t="inlineStr">
-        <is>
-          <t>Нет</t>
-        </is>
-      </c>
-      <c r="L92" t="inlineStr">
-        <is>
-          <t>Быстрая</t>
-        </is>
-      </c>
-      <c r="M92" t="inlineStr">
-        <is>
-          <t>Нет возврата</t>
-        </is>
-      </c>
-      <c r="N92" t="inlineStr">
-        <is>
-          <t>Нет</t>
-        </is>
-      </c>
-    </row>
-    <row r="93">
-      <c r="A93" t="n">
-        <v>4624</v>
-      </c>
-      <c r="B93" t="inlineStr">
-        <is>
-          <t xml:space="preserve">#мебельмаркет </t>
-        </is>
-      </c>
-      <c r="C93" t="inlineStr">
-        <is>
-          <t>5.0</t>
-        </is>
-      </c>
-      <c r="D93" t="inlineStr">
-        <is>
-          <t>Очень довольна заказанным у вас диваном! Идеально подошел по размерам и цвету, доставили в тот же день, а сборка прошла быстро и без проблем. Спасибо за высокое качество и доступные цены!</t>
-        </is>
-      </c>
-      <c r="E93" t="inlineStr">
-        <is>
-          <t>позитив</t>
-        </is>
-      </c>
-      <c r="F93" t="inlineStr">
-        <is>
-          <t>нет</t>
-        </is>
-      </c>
-      <c r="G93" t="inlineStr">
-        <is>
-          <t>нет</t>
-        </is>
-      </c>
-      <c r="H93" t="inlineStr">
-        <is>
-          <t>нет возврата</t>
-        </is>
-      </c>
-      <c r="I93" t="inlineStr">
-        <is>
-          <t>мягкая</t>
-        </is>
-      </c>
-      <c r="J93" t="inlineStr">
-        <is>
-          <t>Позитив</t>
-        </is>
-      </c>
-      <c r="K93" t="inlineStr">
-        <is>
-          <t>Нет</t>
-        </is>
-      </c>
-      <c r="L93" t="inlineStr">
-        <is>
-          <t>Быстрая</t>
-        </is>
-      </c>
-      <c r="M93" t="inlineStr">
-        <is>
-          <t>Нет возврата</t>
-        </is>
-      </c>
-      <c r="N93" t="inlineStr">
-        <is>
-          <t>Мягкая</t>
-        </is>
-      </c>
-    </row>
-    <row r="94">
-      <c r="A94" t="n">
-        <v>8268</v>
-      </c>
-      <c r="B94" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Мебель хит </t>
-        </is>
-      </c>
-      <c r="C94" t="inlineStr">
-        <is>
-          <t>1.0</t>
-        </is>
-      </c>
-      <c r="D94" t="inlineStr">
-        <is>
-          <t>Ужасная организация! Заказываешь одно, по факту получаешь другое. Цены меняют на глазах! Оформлять заказы на мебель не научились. Никакой клиентоориентированности. Жалко потраченное время и нервы.
-Больше ни ногой.</t>
-        </is>
-      </c>
-      <c r="E94" t="inlineStr">
-        <is>
-          <t>негатив</t>
-        </is>
-      </c>
-      <c r="F94" t="inlineStr">
-        <is>
-          <t>сервис</t>
-        </is>
-      </c>
-      <c r="G94" t="inlineStr">
-        <is>
-          <t>нет</t>
-        </is>
-      </c>
-      <c r="H94" t="inlineStr">
-        <is>
-          <t>нет возврата</t>
-        </is>
-      </c>
-      <c r="I94" t="inlineStr">
-        <is>
-          <t>нет</t>
-        </is>
-      </c>
-      <c r="J94" t="inlineStr">
-        <is>
-          <t>Негатив</t>
-        </is>
-      </c>
-      <c r="K94" t="inlineStr">
-        <is>
-          <t>Сервис</t>
-        </is>
-      </c>
-      <c r="L94" t="inlineStr">
-        <is>
-          <t>Нет</t>
-        </is>
-      </c>
-      <c r="M94" t="inlineStr">
-        <is>
-          <t>Несоответствие описанию</t>
-        </is>
-      </c>
-      <c r="N94" t="inlineStr">
-        <is>
-          <t>Нет</t>
-        </is>
-      </c>
-    </row>
-    <row r="95">
-      <c r="A95" t="n">
-        <v>7812</v>
-      </c>
-      <c r="B95" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Виктория </t>
-        </is>
-      </c>
-      <c r="C95" t="inlineStr">
-        <is>
-          <t>5.0</t>
-        </is>
-      </c>
-      <c r="D95" t="inlineStr">
-        <is>
-          <t>Хочу сказать большое спасибо мастерам Александру и Ивану за отличную работу, перетяжка дивана выполненна на отлично! Впредь буду обращаться в эту фирму! Выражаю огромную благодарнлсть</t>
-        </is>
-      </c>
-      <c r="E95" t="inlineStr">
-        <is>
-          <t>позитив</t>
-        </is>
-      </c>
-      <c r="F95" t="inlineStr">
-        <is>
-          <t>нет</t>
-        </is>
-      </c>
-      <c r="G95" t="inlineStr">
-        <is>
-          <t>нет</t>
-        </is>
-      </c>
-      <c r="H95" t="inlineStr">
-        <is>
-          <t>нет возврата</t>
-        </is>
-      </c>
-      <c r="I95" t="inlineStr">
-        <is>
-          <t>нет</t>
-        </is>
-      </c>
-      <c r="J95" t="inlineStr">
-        <is>
-          <t>Позитив</t>
-        </is>
-      </c>
-      <c r="K95" t="inlineStr">
-        <is>
-          <t>Нет</t>
-        </is>
-      </c>
-      <c r="L95" t="inlineStr">
-        <is>
-          <t>Нет</t>
-        </is>
-      </c>
-      <c r="M95" t="inlineStr">
-        <is>
-          <t>Нет возврата</t>
-        </is>
-      </c>
-      <c r="N95" t="inlineStr">
-        <is>
-          <t>Мягкая</t>
-        </is>
-      </c>
-    </row>
-    <row r="96">
-      <c r="A96" t="n">
-        <v>12432</v>
-      </c>
-      <c r="B96" t="inlineStr">
-        <is>
-          <t>По щучьему велению!</t>
-        </is>
-      </c>
-      <c r="C96" t="inlineStr">
-        <is>
-          <t>4 звезды</t>
-        </is>
-      </c>
-      <c r="D96" t="inlineStr">
-        <is>
-          <t>Мне нравиться магазин абсолют</t>
-        </is>
-      </c>
-      <c r="E96" t="inlineStr">
-        <is>
-          <t>нейтрально</t>
-        </is>
-      </c>
-      <c r="F96" t="inlineStr">
-        <is>
-          <t>нет</t>
-        </is>
-      </c>
-      <c r="G96" t="inlineStr">
-        <is>
-          <t>нет</t>
-        </is>
-      </c>
-      <c r="H96" t="inlineStr">
-        <is>
-          <t>нет возврата</t>
-        </is>
-      </c>
-      <c r="I96" t="inlineStr">
-        <is>
-          <t>нет</t>
-        </is>
-      </c>
-      <c r="J96" t="inlineStr">
-        <is>
-          <t>Позитив</t>
-        </is>
-      </c>
-      <c r="K96" t="inlineStr">
-        <is>
-          <t>Нет</t>
-        </is>
-      </c>
-      <c r="L96" t="inlineStr">
-        <is>
-          <t>Нет</t>
-        </is>
-      </c>
-      <c r="M96" t="inlineStr">
-        <is>
-          <t>Нет возврата</t>
-        </is>
-      </c>
-      <c r="N96" t="inlineStr">
-        <is>
-          <t>Нет</t>
-        </is>
-      </c>
-    </row>
-    <row r="97">
-      <c r="A97" t="n">
-        <v>7639</v>
-      </c>
-      <c r="B97" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Алекон </t>
-        </is>
-      </c>
-      <c r="C97" t="inlineStr">
-        <is>
-          <t>5.0</t>
-        </is>
-      </c>
-      <c r="D97" t="inlineStr">
-        <is>
-          <t>Ребята молодцы все очень красиво и аккуратно</t>
-        </is>
-      </c>
-      <c r="E97" t="inlineStr">
-        <is>
-          <t>позитив</t>
-        </is>
-      </c>
-      <c r="F97" t="inlineStr">
-        <is>
-          <t>нет</t>
-        </is>
-      </c>
-      <c r="G97" t="inlineStr">
-        <is>
-          <t>нет</t>
-        </is>
-      </c>
-      <c r="H97" t="inlineStr">
-        <is>
-          <t>нет возврата</t>
-        </is>
-      </c>
-      <c r="I97" t="inlineStr">
-        <is>
-          <t>нет</t>
-        </is>
-      </c>
-      <c r="J97" t="inlineStr">
-        <is>
-          <t>Позитив</t>
-        </is>
-      </c>
-      <c r="K97" t="inlineStr">
-        <is>
-          <t>Нет</t>
-        </is>
-      </c>
-      <c r="L97" t="inlineStr">
-        <is>
-          <t>Нет</t>
-        </is>
-      </c>
-      <c r="M97" t="inlineStr">
-        <is>
-          <t>Нет возврата</t>
-        </is>
-      </c>
-      <c r="N97" t="inlineStr">
-        <is>
-          <t>Нет</t>
-        </is>
-      </c>
-    </row>
-    <row r="98">
-      <c r="A98" t="n">
-        <v>12717</v>
-      </c>
-      <c r="B98" t="inlineStr">
-        <is>
-          <t>Атриум, студия детской мебели</t>
-        </is>
-      </c>
-      <c r="C98" t="inlineStr">
-        <is>
-          <t>2 звезды</t>
-        </is>
-      </c>
-      <c r="D98" t="inlineStr">
-        <is>
-          <t>Дорого</t>
-        </is>
-      </c>
-      <c r="E98" t="inlineStr">
-        <is>
-          <t>нейтрально</t>
-        </is>
-      </c>
-      <c r="F98" t="inlineStr">
-        <is>
-          <t>нет</t>
-        </is>
-      </c>
-      <c r="G98" t="inlineStr">
-        <is>
-          <t>нет</t>
-        </is>
-      </c>
-      <c r="H98" t="inlineStr">
-        <is>
-          <t>нет возврата</t>
-        </is>
-      </c>
-      <c r="I98" t="inlineStr">
-        <is>
-          <t>нет</t>
-        </is>
-      </c>
-      <c r="J98" t="inlineStr">
-        <is>
-          <t>Негатив</t>
-        </is>
-      </c>
-      <c r="K98" t="inlineStr">
-        <is>
-          <t>Иное</t>
-        </is>
-      </c>
-      <c r="L98" t="inlineStr">
-        <is>
-          <t>Нет</t>
-        </is>
-      </c>
-      <c r="M98" t="inlineStr">
-        <is>
-          <t>Нет возврата</t>
-        </is>
-      </c>
-      <c r="N98" t="inlineStr">
-        <is>
-          <t>Нет</t>
-        </is>
-      </c>
-    </row>
-    <row r="99">
-      <c r="A99" t="n">
-        <v>1351</v>
-      </c>
-      <c r="B99" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Nordeagle Mebel </t>
-        </is>
-      </c>
-      <c r="C99" t="inlineStr">
-        <is>
-          <t>5.0</t>
-        </is>
-      </c>
-      <c r="D99" t="inlineStr">
-        <is>
-          <t>Все классно, очень довольны, не смотря на позднюю доставку.</t>
-        </is>
-      </c>
-      <c r="E99" t="inlineStr">
-        <is>
-          <t>позитив</t>
-        </is>
-      </c>
-      <c r="F99" t="inlineStr">
-        <is>
-          <t>нет</t>
-        </is>
-      </c>
-      <c r="G99" t="inlineStr">
-        <is>
-          <t>медленная</t>
-        </is>
-      </c>
-      <c r="H99" t="inlineStr">
-        <is>
-          <t>нет возврата</t>
-        </is>
-      </c>
-      <c r="I99" t="inlineStr">
-        <is>
-          <t>нет</t>
-        </is>
-      </c>
-      <c r="J99" t="inlineStr">
-        <is>
-          <t>Позитив</t>
-        </is>
-      </c>
-      <c r="K99" t="inlineStr">
-        <is>
-          <t>Нет</t>
-        </is>
-      </c>
-      <c r="L99" t="inlineStr">
-        <is>
-          <t>Медленная</t>
-        </is>
-      </c>
-      <c r="M99" t="inlineStr">
-        <is>
-          <t>Нет возврата</t>
-        </is>
-      </c>
-      <c r="N99" t="inlineStr">
-        <is>
-          <t>Нет</t>
-        </is>
-      </c>
-    </row>
-    <row r="100">
-      <c r="A100" t="n">
-        <v>4749</v>
-      </c>
-      <c r="B100" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Много Мебели </t>
-        </is>
-      </c>
-      <c r="C100" t="inlineStr">
-        <is>
-          <t>3.0</t>
-        </is>
-      </c>
-      <c r="D100" t="inlineStr">
         <is>
           <t>До оплаты товара у вас не возникнет никаких проблем, но после готовьтесь столкнуться с кучей бюрократии.
 Сервис должен быть удобный, но у этого магазина видимо другое мнение.
@@ -7024,6 +6824,566 @@
 Попробую написать на почту, если ответа не последует и мне не отдадут товар, то оценку изменю ещё ниже.</t>
         </is>
       </c>
+      <c r="E92" t="inlineStr">
+        <is>
+          <t>негатив</t>
+        </is>
+      </c>
+      <c r="F92" t="inlineStr">
+        <is>
+          <t>сервис</t>
+        </is>
+      </c>
+      <c r="G92" t="inlineStr">
+        <is>
+          <t>нет</t>
+        </is>
+      </c>
+      <c r="H92" t="inlineStr">
+        <is>
+          <t>нет возврата</t>
+        </is>
+      </c>
+      <c r="I92" t="inlineStr">
+        <is>
+          <t>нет</t>
+        </is>
+      </c>
+      <c r="J92" t="inlineStr">
+        <is>
+          <t>Негатив</t>
+        </is>
+      </c>
+      <c r="K92" t="inlineStr">
+        <is>
+          <t>Сервис</t>
+        </is>
+      </c>
+      <c r="L92" t="inlineStr">
+        <is>
+          <t>Нет</t>
+        </is>
+      </c>
+      <c r="M92" t="inlineStr">
+        <is>
+          <t>Нет возврата</t>
+        </is>
+      </c>
+      <c r="N92" t="inlineStr">
+        <is>
+          <t>Нет</t>
+        </is>
+      </c>
+    </row>
+    <row r="93">
+      <c r="A93" t="n">
+        <v>4739</v>
+      </c>
+      <c r="B93" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Много Мебели </t>
+        </is>
+      </c>
+      <c r="C93" t="inlineStr">
+        <is>
+          <t>5.0</t>
+        </is>
+      </c>
+      <c r="D93" t="inlineStr">
+        <is>
+          <t>Торговая сеть Много Мебели мне известна еще с 2019 года, тогда у знакомых появился их диван, с тех пор чего только там не покупалось от стульев до кровати</t>
+        </is>
+      </c>
+      <c r="E93" t="inlineStr">
+        <is>
+          <t>позитив</t>
+        </is>
+      </c>
+      <c r="F93" t="inlineStr">
+        <is>
+          <t>нет</t>
+        </is>
+      </c>
+      <c r="G93" t="inlineStr">
+        <is>
+          <t>нет</t>
+        </is>
+      </c>
+      <c r="H93" t="inlineStr">
+        <is>
+          <t>нет возврата</t>
+        </is>
+      </c>
+      <c r="I93" t="inlineStr">
+        <is>
+          <t>мягкая</t>
+        </is>
+      </c>
+      <c r="J93" t="inlineStr">
+        <is>
+          <t>Позитив</t>
+        </is>
+      </c>
+      <c r="K93" t="inlineStr">
+        <is>
+          <t>Нет</t>
+        </is>
+      </c>
+      <c r="L93" t="inlineStr">
+        <is>
+          <t>Нет</t>
+        </is>
+      </c>
+      <c r="M93" t="inlineStr">
+        <is>
+          <t>Нет возврата</t>
+        </is>
+      </c>
+      <c r="N93" t="inlineStr">
+        <is>
+          <t>Мягкая</t>
+        </is>
+      </c>
+    </row>
+    <row r="94">
+      <c r="A94" t="n">
+        <v>1060</v>
+      </c>
+      <c r="B94" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Магазин эконом-мебели </t>
+        </is>
+      </c>
+      <c r="C94" t="inlineStr">
+        <is>
+          <t>1.0</t>
+        </is>
+      </c>
+      <c r="D94" t="inlineStr">
+        <is>
+          <t>Приобрели с женой шкаф-пенал в данной компании. Подкупила стоимость, показалась изначально невысокой, да и название фирмы это подтверждало. Когда распаковывали товар - обнаружили приличный брак, устанавливать шкаф с таким дефектом совсем не было желания. Сразу же обратились в компанию с претензией. По телефону нам сообщили, что на следующий день данная деталь будет заменена на новую. Обещание так и не выполнили, каждый последующий день отодвигали сроки. В итоге через неделю мы отвезли шкаф обратно в магазин и потребовали возврата денежных средств (на этот момент нами уже был куплен новый шкаф, лучшего качества и по более низкой цене). В настоящее время продавец деньги за шкаф так и не вернул, уже прошли все сроки, установленные законом</t>
+        </is>
+      </c>
+      <c r="E94" t="inlineStr">
+        <is>
+          <t>негатив</t>
+        </is>
+      </c>
+      <c r="F94" t="inlineStr">
+        <is>
+          <t>качество</t>
+        </is>
+      </c>
+      <c r="G94" t="inlineStr">
+        <is>
+          <t>нет</t>
+        </is>
+      </c>
+      <c r="H94" t="inlineStr">
+        <is>
+          <t>брак</t>
+        </is>
+      </c>
+      <c r="I94" t="inlineStr">
+        <is>
+          <t>корпусная</t>
+        </is>
+      </c>
+      <c r="J94" t="inlineStr">
+        <is>
+          <t>Негатив</t>
+        </is>
+      </c>
+      <c r="K94" t="inlineStr">
+        <is>
+          <t>Сервис</t>
+        </is>
+      </c>
+      <c r="L94" t="inlineStr">
+        <is>
+          <t>Нет</t>
+        </is>
+      </c>
+      <c r="M94" t="inlineStr">
+        <is>
+          <t>Брак</t>
+        </is>
+      </c>
+      <c r="N94" t="inlineStr">
+        <is>
+          <t>Корпусная</t>
+        </is>
+      </c>
+    </row>
+    <row r="95">
+      <c r="A95" t="n">
+        <v>8841</v>
+      </c>
+      <c r="B95" t="inlineStr">
+        <is>
+          <t>Планета Мебели</t>
+        </is>
+      </c>
+      <c r="C95" t="inlineStr">
+        <is>
+          <t>3.0</t>
+        </is>
+      </c>
+      <c r="D95" t="inlineStr">
+        <is>
+          <t>Мебель недорогая,среднего качества,купили стенку,при сборке не хватило коробки и одна деталь оказалась с браком,менять бесплатно отказались,только платить деньги и ждать деталь 7 дней,сказали: надо было сборку нашу заказывать…🤔там кого было бы собирать?! Хотели там ещё дочери гарнитур купить и кровать и кухню,но именно столкнувшись с обслуживанием в мелочах,отказались больше здесь покупать.. нашли более приятный в обслуживании клиентов салон 😊</t>
+        </is>
+      </c>
+      <c r="E95" t="inlineStr">
+        <is>
+          <t>негатив</t>
+        </is>
+      </c>
+      <c r="F95" t="inlineStr">
+        <is>
+          <t>сервис</t>
+        </is>
+      </c>
+      <c r="G95" t="inlineStr">
+        <is>
+          <t>нет</t>
+        </is>
+      </c>
+      <c r="H95" t="inlineStr">
+        <is>
+          <t>брак</t>
+        </is>
+      </c>
+      <c r="I95" t="inlineStr">
+        <is>
+          <t>корпусная</t>
+        </is>
+      </c>
+      <c r="J95" t="inlineStr">
+        <is>
+          <t>Негатив</t>
+        </is>
+      </c>
+      <c r="K95" t="inlineStr">
+        <is>
+          <t>Сервис</t>
+        </is>
+      </c>
+      <c r="L95" t="inlineStr">
+        <is>
+          <t>Нет</t>
+        </is>
+      </c>
+      <c r="M95" t="inlineStr">
+        <is>
+          <t>Брак</t>
+        </is>
+      </c>
+      <c r="N95" t="inlineStr">
+        <is>
+          <t>Корпусная</t>
+        </is>
+      </c>
+    </row>
+    <row r="96">
+      <c r="A96" t="n">
+        <v>1784</v>
+      </c>
+      <c r="B96" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Lazurit </t>
+        </is>
+      </c>
+      <c r="C96" t="inlineStr">
+        <is>
+          <t>1.0</t>
+        </is>
+      </c>
+      <c r="D96" t="inlineStr">
+        <is>
+          <t>Брали диван, оказался бракованный, устранили в течении года. Внимательнее смотрите при покупке мебель. Сервис отвратительный.</t>
+        </is>
+      </c>
+      <c r="E96" t="inlineStr">
+        <is>
+          <t>негатив</t>
+        </is>
+      </c>
+      <c r="F96" t="inlineStr">
+        <is>
+          <t>сервис</t>
+        </is>
+      </c>
+      <c r="G96" t="inlineStr">
+        <is>
+          <t>нет</t>
+        </is>
+      </c>
+      <c r="H96" t="inlineStr">
+        <is>
+          <t>брак</t>
+        </is>
+      </c>
+      <c r="I96" t="inlineStr">
+        <is>
+          <t>мягкая</t>
+        </is>
+      </c>
+      <c r="J96" t="inlineStr">
+        <is>
+          <t>Негатив</t>
+        </is>
+      </c>
+      <c r="K96" t="inlineStr">
+        <is>
+          <t>Сервис</t>
+        </is>
+      </c>
+      <c r="L96" t="inlineStr">
+        <is>
+          <t>Нет</t>
+        </is>
+      </c>
+      <c r="M96" t="inlineStr">
+        <is>
+          <t>Брак</t>
+        </is>
+      </c>
+      <c r="N96" t="inlineStr">
+        <is>
+          <t>Мягкая</t>
+        </is>
+      </c>
+    </row>
+    <row r="97">
+      <c r="A97" t="n">
+        <v>1853</v>
+      </c>
+      <c r="B97" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Lazurit </t>
+        </is>
+      </c>
+      <c r="C97" t="inlineStr">
+        <is>
+          <t>1.0</t>
+        </is>
+      </c>
+      <c r="D97" t="inlineStr">
+        <is>
+          <t>Лазурит, худший магазин в котором заказывали мебель, не покупайте там мебель, денег своих не стоит, да ещё и сервис хромает. Мебель в феврале пришла сломанной, в договоре написано, что устраняют брак за 45 дней, сейчас конец мая, до сих пор ничего не заменено. Сегодня позвонили, целый день жду сборку, время 20:00, их нет. Люди не покупайте в Лазурите, одни проблемы с этим магазином. Лазурит не оправдал, то качество мебели и Сервиса с которым он себя позиционирует.Хуже быть не может.</t>
+        </is>
+      </c>
+      <c r="E97" t="inlineStr">
+        <is>
+          <t>негатив</t>
+        </is>
+      </c>
+      <c r="F97" t="inlineStr">
+        <is>
+          <t>сервис</t>
+        </is>
+      </c>
+      <c r="G97" t="inlineStr">
+        <is>
+          <t>нет</t>
+        </is>
+      </c>
+      <c r="H97" t="inlineStr">
+        <is>
+          <t>брак</t>
+        </is>
+      </c>
+      <c r="I97" t="inlineStr">
+        <is>
+          <t>нет</t>
+        </is>
+      </c>
+      <c r="J97" t="inlineStr">
+        <is>
+          <t>Негатив</t>
+        </is>
+      </c>
+      <c r="K97" t="inlineStr">
+        <is>
+          <t>Сервис, Качество</t>
+        </is>
+      </c>
+      <c r="L97" t="inlineStr">
+        <is>
+          <t>Нет</t>
+        </is>
+      </c>
+      <c r="M97" t="inlineStr">
+        <is>
+          <t>Брак</t>
+        </is>
+      </c>
+      <c r="N97" t="inlineStr">
+        <is>
+          <t>Нет</t>
+        </is>
+      </c>
+    </row>
+    <row r="98">
+      <c r="A98" t="n">
+        <v>3458</v>
+      </c>
+      <c r="B98" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Bravo Mebel </t>
+        </is>
+      </c>
+      <c r="C98" t="inlineStr">
+        <is>
+          <t>1.0</t>
+        </is>
+      </c>
+      <c r="D98" t="inlineStr">
+        <is>
+          <t>Ужасная фирма , прошу к ним не обращаться , ни за кухней не зачем потом пожалеете , об этом . Мы взяли кухню мойка оказалась брак , менять отказываются . На них очень много жалоб , они судятся постоянно . Жаль , что мы не узнали об этом раньше .</t>
+        </is>
+      </c>
+      <c r="E98" t="inlineStr">
+        <is>
+          <t>негатив</t>
+        </is>
+      </c>
+      <c r="F98" t="inlineStr">
+        <is>
+          <t>сервис</t>
+        </is>
+      </c>
+      <c r="G98" t="inlineStr">
+        <is>
+          <t>нет</t>
+        </is>
+      </c>
+      <c r="H98" t="inlineStr">
+        <is>
+          <t>брак</t>
+        </is>
+      </c>
+      <c r="I98" t="inlineStr">
+        <is>
+          <t>корпусная</t>
+        </is>
+      </c>
+      <c r="J98" t="inlineStr">
+        <is>
+          <t>Негатив</t>
+        </is>
+      </c>
+      <c r="K98" t="inlineStr">
+        <is>
+          <t>Качество</t>
+        </is>
+      </c>
+      <c r="L98" t="inlineStr">
+        <is>
+          <t>Нет</t>
+        </is>
+      </c>
+      <c r="M98" t="inlineStr">
+        <is>
+          <t>Брак</t>
+        </is>
+      </c>
+      <c r="N98" t="inlineStr">
+        <is>
+          <t>Корпусная</t>
+        </is>
+      </c>
+    </row>
+    <row r="99">
+      <c r="A99" t="n">
+        <v>4406</v>
+      </c>
+      <c r="B99" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Союз 38 Текс </t>
+        </is>
+      </c>
+      <c r="C99" t="inlineStr">
+        <is>
+          <t>1.0</t>
+        </is>
+      </c>
+      <c r="D99" t="inlineStr">
+        <is>
+          <t>Продали бракованный каркас, обменять или вернуть деньги отказались,сказали это вы сломали.....</t>
+        </is>
+      </c>
+      <c r="E99" t="inlineStr">
+        <is>
+          <t>негатив</t>
+        </is>
+      </c>
+      <c r="F99" t="inlineStr">
+        <is>
+          <t>сервис</t>
+        </is>
+      </c>
+      <c r="G99" t="inlineStr">
+        <is>
+          <t>нет</t>
+        </is>
+      </c>
+      <c r="H99" t="inlineStr">
+        <is>
+          <t>брак</t>
+        </is>
+      </c>
+      <c r="I99" t="inlineStr">
+        <is>
+          <t>нет</t>
+        </is>
+      </c>
+      <c r="J99" t="inlineStr">
+        <is>
+          <t>Негатив</t>
+        </is>
+      </c>
+      <c r="K99" t="inlineStr">
+        <is>
+          <t>Качество</t>
+        </is>
+      </c>
+      <c r="L99" t="inlineStr">
+        <is>
+          <t>Нет</t>
+        </is>
+      </c>
+      <c r="M99" t="inlineStr">
+        <is>
+          <t>Брак</t>
+        </is>
+      </c>
+      <c r="N99" t="inlineStr">
+        <is>
+          <t>Корпусная</t>
+        </is>
+      </c>
+    </row>
+    <row r="100">
+      <c r="A100" t="n">
+        <v>6490</v>
+      </c>
+      <c r="B100" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Много Мебели </t>
+        </is>
+      </c>
+      <c r="C100" t="inlineStr">
+        <is>
+          <t>1.0</t>
+        </is>
+      </c>
+      <c r="D100" t="inlineStr">
+        <is>
+          <t>Жаль, что поставить оценку ниже нельзя. Оценка не салону мебели, а именно компании "много мебели". Заказ оформлен в декабре, на 29 марта стенка не собрана по причине брака. С руководством связаться невозможно. Все вопросы решаются через посредников, сидящих в колл-центре. Ответственности за свою работу никто не несёт. Позорище, одним словом.</t>
+        </is>
+      </c>
       <c r="E100" t="inlineStr">
         <is>
           <t>негатив</t>
@@ -7041,12 +7401,12 @@
       </c>
       <c r="H100" t="inlineStr">
         <is>
-          <t>нет возврата</t>
+          <t>брак</t>
         </is>
       </c>
       <c r="I100" t="inlineStr">
         <is>
-          <t>нет</t>
+          <t>корпусная</t>
         </is>
       </c>
       <c r="J100" t="inlineStr">
@@ -7066,82 +7426,12 @@
       </c>
       <c r="M100" t="inlineStr">
         <is>
-          <t>Нет возврата</t>
+          <t>Брак</t>
         </is>
       </c>
       <c r="N100" t="inlineStr">
         <is>
-          <t>Нет</t>
-        </is>
-      </c>
-    </row>
-    <row r="101">
-      <c r="A101" t="n">
-        <v>4739</v>
-      </c>
-      <c r="B101" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Много Мебели </t>
-        </is>
-      </c>
-      <c r="C101" t="inlineStr">
-        <is>
-          <t>5.0</t>
-        </is>
-      </c>
-      <c r="D101" t="inlineStr">
-        <is>
-          <t>Торговая сеть Много Мебели мне известна еще с 2019 года, тогда у знакомых появился их диван, с тех пор чего только там не покупалось от стульев до кровати</t>
-        </is>
-      </c>
-      <c r="E101" t="inlineStr">
-        <is>
-          <t>позитив</t>
-        </is>
-      </c>
-      <c r="F101" t="inlineStr">
-        <is>
-          <t>нет</t>
-        </is>
-      </c>
-      <c r="G101" t="inlineStr">
-        <is>
-          <t>нет</t>
-        </is>
-      </c>
-      <c r="H101" t="inlineStr">
-        <is>
-          <t>нет возврата</t>
-        </is>
-      </c>
-      <c r="I101" t="inlineStr">
-        <is>
-          <t>мягкая</t>
-        </is>
-      </c>
-      <c r="J101" t="inlineStr">
-        <is>
-          <t>Позитив</t>
-        </is>
-      </c>
-      <c r="K101" t="inlineStr">
-        <is>
-          <t>Нет</t>
-        </is>
-      </c>
-      <c r="L101" t="inlineStr">
-        <is>
-          <t>Нет</t>
-        </is>
-      </c>
-      <c r="M101" t="inlineStr">
-        <is>
-          <t>Нет возврата</t>
-        </is>
-      </c>
-      <c r="N101" t="inlineStr">
-        <is>
-          <t>Мягкая</t>
+          <t>Корпусная</t>
         </is>
       </c>
     </row>
